--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67A07B2-E1BD-4B01-867C-DAB4D94904E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAA3CB6-A6B9-4504-BA54-375BE301B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -56001,8 +56001,8 @@
       <c r="CJ122">
         <v>13</v>
       </c>
-      <c r="CK122" s="4">
-        <v>0</v>
+      <c r="CK122">
+        <v>13</v>
       </c>
       <c r="CL122" s="4">
         <v>0</v>
@@ -56061,8 +56061,8 @@
       <c r="DD122" s="4">
         <v>0</v>
       </c>
-      <c r="DE122">
-        <v>13</v>
+      <c r="DE122" s="4">
+        <v>0</v>
       </c>
       <c r="DF122">
         <v>13</v>
@@ -56453,8 +56453,8 @@
       <c r="CJ123">
         <v>13</v>
       </c>
-      <c r="CK123" s="4">
-        <v>0</v>
+      <c r="CK123">
+        <v>13</v>
       </c>
       <c r="CL123" s="4">
         <v>0</v>
@@ -56513,8 +56513,8 @@
       <c r="DD123" s="4">
         <v>0</v>
       </c>
-      <c r="DE123">
-        <v>13</v>
+      <c r="DE123" s="4">
+        <v>0</v>
       </c>
       <c r="DF123">
         <v>13</v>
@@ -56905,8 +56905,8 @@
       <c r="CJ124">
         <v>13</v>
       </c>
-      <c r="CK124" s="4">
-        <v>0</v>
+      <c r="CK124">
+        <v>13</v>
       </c>
       <c r="CL124" s="4">
         <v>0</v>
@@ -56965,8 +56965,8 @@
       <c r="DD124" s="4">
         <v>0</v>
       </c>
-      <c r="DE124">
-        <v>13</v>
+      <c r="DE124" s="4">
+        <v>0</v>
       </c>
       <c r="DF124">
         <v>13</v>
@@ -57357,8 +57357,8 @@
       <c r="CJ125">
         <v>13</v>
       </c>
-      <c r="CK125" s="4">
-        <v>0</v>
+      <c r="CK125">
+        <v>13</v>
       </c>
       <c r="CL125" s="4">
         <v>0</v>
@@ -57417,8 +57417,8 @@
       <c r="DD125" s="4">
         <v>0</v>
       </c>
-      <c r="DE125">
-        <v>13</v>
+      <c r="DE125" s="4">
+        <v>0</v>
       </c>
       <c r="DF125">
         <v>13</v>
@@ -57809,8 +57809,8 @@
       <c r="CJ126">
         <v>13</v>
       </c>
-      <c r="CK126" s="4">
-        <v>0</v>
+      <c r="CK126">
+        <v>13</v>
       </c>
       <c r="CL126" s="4">
         <v>0</v>
@@ -57869,8 +57869,8 @@
       <c r="DD126" s="4">
         <v>0</v>
       </c>
-      <c r="DE126">
-        <v>13</v>
+      <c r="DE126" s="4">
+        <v>0</v>
       </c>
       <c r="DF126">
         <v>13</v>
@@ -58261,8 +58261,8 @@
       <c r="CJ127">
         <v>13</v>
       </c>
-      <c r="CK127" s="4">
-        <v>0</v>
+      <c r="CK127">
+        <v>13</v>
       </c>
       <c r="CL127" s="4">
         <v>0</v>
@@ -58321,8 +58321,8 @@
       <c r="DD127" s="4">
         <v>0</v>
       </c>
-      <c r="DE127">
-        <v>13</v>
+      <c r="DE127" s="4">
+        <v>0</v>
       </c>
       <c r="DF127">
         <v>13</v>
@@ -58713,8 +58713,8 @@
       <c r="CJ128">
         <v>13</v>
       </c>
-      <c r="CK128" s="4">
-        <v>0</v>
+      <c r="CK128">
+        <v>13</v>
       </c>
       <c r="CL128" s="4">
         <v>0</v>
@@ -58773,8 +58773,8 @@
       <c r="DD128" s="4">
         <v>0</v>
       </c>
-      <c r="DE128">
-        <v>13</v>
+      <c r="DE128" s="4">
+        <v>0</v>
       </c>
       <c r="DF128">
         <v>13</v>
@@ -59165,8 +59165,8 @@
       <c r="CJ129">
         <v>13</v>
       </c>
-      <c r="CK129" s="4">
-        <v>0</v>
+      <c r="CK129">
+        <v>13</v>
       </c>
       <c r="CL129" s="4">
         <v>0</v>
@@ -59225,8 +59225,8 @@
       <c r="DD129" s="4">
         <v>0</v>
       </c>
-      <c r="DE129">
-        <v>13</v>
+      <c r="DE129" s="4">
+        <v>0</v>
       </c>
       <c r="DF129">
         <v>13</v>
@@ -59617,8 +59617,8 @@
       <c r="CJ130">
         <v>13</v>
       </c>
-      <c r="CK130" s="4">
-        <v>0</v>
+      <c r="CK130">
+        <v>13</v>
       </c>
       <c r="CL130" s="4">
         <v>0</v>
@@ -59677,8 +59677,8 @@
       <c r="DD130" s="4">
         <v>0</v>
       </c>
-      <c r="DE130">
-        <v>13</v>
+      <c r="DE130" s="4">
+        <v>0</v>
       </c>
       <c r="DF130">
         <v>13</v>
@@ -60069,8 +60069,8 @@
       <c r="CJ131">
         <v>13</v>
       </c>
-      <c r="CK131" s="4">
-        <v>0</v>
+      <c r="CK131">
+        <v>13</v>
       </c>
       <c r="CL131" s="4">
         <v>0</v>
@@ -60129,8 +60129,8 @@
       <c r="DD131" s="4">
         <v>0</v>
       </c>
-      <c r="DE131">
-        <v>13</v>
+      <c r="DE131" s="4">
+        <v>0</v>
       </c>
       <c r="DF131">
         <v>13</v>
@@ -60521,7 +60521,7 @@
       <c r="CJ132" s="5">
         <v>5</v>
       </c>
-      <c r="CK132" s="4">
+      <c r="CK132" s="5">
         <v>0</v>
       </c>
       <c r="CL132" s="4">
@@ -60549,11 +60549,11 @@
         <v>0</v>
       </c>
       <c r="CT132" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU132" s="4">
         <v>10</v>
       </c>
-      <c r="CU132" s="4">
-        <v>0</v>
-      </c>
       <c r="CV132" s="4">
         <v>0</v>
       </c>
@@ -60581,8 +60581,8 @@
       <c r="DD132" s="4">
         <v>0</v>
       </c>
-      <c r="DE132">
-        <v>13</v>
+      <c r="DE132" s="4">
+        <v>0</v>
       </c>
       <c r="DF132">
         <v>13</v>
@@ -60973,8 +60973,8 @@
       <c r="CJ133">
         <v>13</v>
       </c>
-      <c r="CK133" s="4">
-        <v>0</v>
+      <c r="CK133">
+        <v>13</v>
       </c>
       <c r="CL133" s="4">
         <v>0</v>
@@ -61033,8 +61033,8 @@
       <c r="DD133" s="4">
         <v>0</v>
       </c>
-      <c r="DE133">
-        <v>13</v>
+      <c r="DE133" s="4">
+        <v>0</v>
       </c>
       <c r="DF133">
         <v>13</v>
@@ -61425,8 +61425,8 @@
       <c r="CJ134">
         <v>13</v>
       </c>
-      <c r="CK134" s="4">
-        <v>0</v>
+      <c r="CK134">
+        <v>13</v>
       </c>
       <c r="CL134" s="4">
         <v>0</v>
@@ -61485,8 +61485,8 @@
       <c r="DD134" s="4">
         <v>0</v>
       </c>
-      <c r="DE134">
-        <v>13</v>
+      <c r="DE134" s="4">
+        <v>0</v>
       </c>
       <c r="DF134">
         <v>13</v>
@@ -61877,8 +61877,8 @@
       <c r="CJ135">
         <v>13</v>
       </c>
-      <c r="CK135" s="4">
-        <v>0</v>
+      <c r="CK135">
+        <v>13</v>
       </c>
       <c r="CL135" s="4">
         <v>0</v>
@@ -61937,8 +61937,8 @@
       <c r="DD135" s="4">
         <v>0</v>
       </c>
-      <c r="DE135">
-        <v>13</v>
+      <c r="DE135" s="4">
+        <v>0</v>
       </c>
       <c r="DF135">
         <v>13</v>
@@ -62329,8 +62329,8 @@
       <c r="CJ136">
         <v>13</v>
       </c>
-      <c r="CK136" s="4">
-        <v>0</v>
+      <c r="CK136">
+        <v>13</v>
       </c>
       <c r="CL136" s="4">
         <v>0</v>
@@ -62389,8 +62389,8 @@
       <c r="DD136" s="4">
         <v>0</v>
       </c>
-      <c r="DE136">
-        <v>13</v>
+      <c r="DE136" s="4">
+        <v>0</v>
       </c>
       <c r="DF136">
         <v>13</v>
@@ -62781,8 +62781,8 @@
       <c r="CJ137">
         <v>13</v>
       </c>
-      <c r="CK137" s="4">
-        <v>0</v>
+      <c r="CK137">
+        <v>13</v>
       </c>
       <c r="CL137" s="4">
         <v>0</v>
@@ -62841,8 +62841,8 @@
       <c r="DD137" s="4">
         <v>0</v>
       </c>
-      <c r="DE137">
-        <v>13</v>
+      <c r="DE137" s="4">
+        <v>0</v>
       </c>
       <c r="DF137">
         <v>13</v>
@@ -63233,8 +63233,8 @@
       <c r="CJ138">
         <v>13</v>
       </c>
-      <c r="CK138" s="4">
-        <v>0</v>
+      <c r="CK138">
+        <v>13</v>
       </c>
       <c r="CL138" s="4">
         <v>0</v>
@@ -63293,8 +63293,8 @@
       <c r="DD138" s="4">
         <v>0</v>
       </c>
-      <c r="DE138">
-        <v>13</v>
+      <c r="DE138" s="4">
+        <v>0</v>
       </c>
       <c r="DF138">
         <v>13</v>
@@ -63685,8 +63685,8 @@
       <c r="CJ139">
         <v>13</v>
       </c>
-      <c r="CK139" s="4">
-        <v>0</v>
+      <c r="CK139">
+        <v>13</v>
       </c>
       <c r="CL139" s="4">
         <v>0</v>
@@ -63745,8 +63745,8 @@
       <c r="DD139" s="4">
         <v>0</v>
       </c>
-      <c r="DE139">
-        <v>13</v>
+      <c r="DE139" s="4">
+        <v>0</v>
       </c>
       <c r="DF139">
         <v>13</v>
@@ -64137,9 +64137,6 @@
       <c r="CJ140">
         <v>13</v>
       </c>
-      <c r="CK140" s="4">
-        <v>0</v>
-      </c>
       <c r="CL140" s="4">
         <v>0</v>
       </c>
@@ -64197,8 +64194,8 @@
       <c r="DD140" s="4">
         <v>0</v>
       </c>
-      <c r="DE140">
-        <v>13</v>
+      <c r="DE140" s="4">
+        <v>0</v>
       </c>
       <c r="DF140">
         <v>13</v>
@@ -64589,9 +64586,6 @@
       <c r="CJ141">
         <v>13</v>
       </c>
-      <c r="CK141" s="4">
-        <v>0</v>
-      </c>
       <c r="CL141" s="4">
         <v>0</v>
       </c>
@@ -64649,8 +64643,8 @@
       <c r="DD141" s="4">
         <v>0</v>
       </c>
-      <c r="DE141">
-        <v>13</v>
+      <c r="DE141" s="4">
+        <v>0</v>
       </c>
       <c r="DF141">
         <v>13</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAA3CB6-A6B9-4504-BA54-375BE301B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67A07B2-E1BD-4B01-867C-DAB4D94904E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -56001,8 +56001,8 @@
       <c r="CJ122">
         <v>13</v>
       </c>
-      <c r="CK122">
-        <v>13</v>
+      <c r="CK122" s="4">
+        <v>0</v>
       </c>
       <c r="CL122" s="4">
         <v>0</v>
@@ -56061,8 +56061,8 @@
       <c r="DD122" s="4">
         <v>0</v>
       </c>
-      <c r="DE122" s="4">
-        <v>0</v>
+      <c r="DE122">
+        <v>13</v>
       </c>
       <c r="DF122">
         <v>13</v>
@@ -56453,8 +56453,8 @@
       <c r="CJ123">
         <v>13</v>
       </c>
-      <c r="CK123">
-        <v>13</v>
+      <c r="CK123" s="4">
+        <v>0</v>
       </c>
       <c r="CL123" s="4">
         <v>0</v>
@@ -56513,8 +56513,8 @@
       <c r="DD123" s="4">
         <v>0</v>
       </c>
-      <c r="DE123" s="4">
-        <v>0</v>
+      <c r="DE123">
+        <v>13</v>
       </c>
       <c r="DF123">
         <v>13</v>
@@ -56905,8 +56905,8 @@
       <c r="CJ124">
         <v>13</v>
       </c>
-      <c r="CK124">
-        <v>13</v>
+      <c r="CK124" s="4">
+        <v>0</v>
       </c>
       <c r="CL124" s="4">
         <v>0</v>
@@ -56965,8 +56965,8 @@
       <c r="DD124" s="4">
         <v>0</v>
       </c>
-      <c r="DE124" s="4">
-        <v>0</v>
+      <c r="DE124">
+        <v>13</v>
       </c>
       <c r="DF124">
         <v>13</v>
@@ -57357,8 +57357,8 @@
       <c r="CJ125">
         <v>13</v>
       </c>
-      <c r="CK125">
-        <v>13</v>
+      <c r="CK125" s="4">
+        <v>0</v>
       </c>
       <c r="CL125" s="4">
         <v>0</v>
@@ -57417,8 +57417,8 @@
       <c r="DD125" s="4">
         <v>0</v>
       </c>
-      <c r="DE125" s="4">
-        <v>0</v>
+      <c r="DE125">
+        <v>13</v>
       </c>
       <c r="DF125">
         <v>13</v>
@@ -57809,8 +57809,8 @@
       <c r="CJ126">
         <v>13</v>
       </c>
-      <c r="CK126">
-        <v>13</v>
+      <c r="CK126" s="4">
+        <v>0</v>
       </c>
       <c r="CL126" s="4">
         <v>0</v>
@@ -57869,8 +57869,8 @@
       <c r="DD126" s="4">
         <v>0</v>
       </c>
-      <c r="DE126" s="4">
-        <v>0</v>
+      <c r="DE126">
+        <v>13</v>
       </c>
       <c r="DF126">
         <v>13</v>
@@ -58261,8 +58261,8 @@
       <c r="CJ127">
         <v>13</v>
       </c>
-      <c r="CK127">
-        <v>13</v>
+      <c r="CK127" s="4">
+        <v>0</v>
       </c>
       <c r="CL127" s="4">
         <v>0</v>
@@ -58321,8 +58321,8 @@
       <c r="DD127" s="4">
         <v>0</v>
       </c>
-      <c r="DE127" s="4">
-        <v>0</v>
+      <c r="DE127">
+        <v>13</v>
       </c>
       <c r="DF127">
         <v>13</v>
@@ -58713,8 +58713,8 @@
       <c r="CJ128">
         <v>13</v>
       </c>
-      <c r="CK128">
-        <v>13</v>
+      <c r="CK128" s="4">
+        <v>0</v>
       </c>
       <c r="CL128" s="4">
         <v>0</v>
@@ -58773,8 +58773,8 @@
       <c r="DD128" s="4">
         <v>0</v>
       </c>
-      <c r="DE128" s="4">
-        <v>0</v>
+      <c r="DE128">
+        <v>13</v>
       </c>
       <c r="DF128">
         <v>13</v>
@@ -59165,8 +59165,8 @@
       <c r="CJ129">
         <v>13</v>
       </c>
-      <c r="CK129">
-        <v>13</v>
+      <c r="CK129" s="4">
+        <v>0</v>
       </c>
       <c r="CL129" s="4">
         <v>0</v>
@@ -59225,8 +59225,8 @@
       <c r="DD129" s="4">
         <v>0</v>
       </c>
-      <c r="DE129" s="4">
-        <v>0</v>
+      <c r="DE129">
+        <v>13</v>
       </c>
       <c r="DF129">
         <v>13</v>
@@ -59617,8 +59617,8 @@
       <c r="CJ130">
         <v>13</v>
       </c>
-      <c r="CK130">
-        <v>13</v>
+      <c r="CK130" s="4">
+        <v>0</v>
       </c>
       <c r="CL130" s="4">
         <v>0</v>
@@ -59677,8 +59677,8 @@
       <c r="DD130" s="4">
         <v>0</v>
       </c>
-      <c r="DE130" s="4">
-        <v>0</v>
+      <c r="DE130">
+        <v>13</v>
       </c>
       <c r="DF130">
         <v>13</v>
@@ -60069,8 +60069,8 @@
       <c r="CJ131">
         <v>13</v>
       </c>
-      <c r="CK131">
-        <v>13</v>
+      <c r="CK131" s="4">
+        <v>0</v>
       </c>
       <c r="CL131" s="4">
         <v>0</v>
@@ -60129,8 +60129,8 @@
       <c r="DD131" s="4">
         <v>0</v>
       </c>
-      <c r="DE131" s="4">
-        <v>0</v>
+      <c r="DE131">
+        <v>13</v>
       </c>
       <c r="DF131">
         <v>13</v>
@@ -60521,7 +60521,7 @@
       <c r="CJ132" s="5">
         <v>5</v>
       </c>
-      <c r="CK132" s="5">
+      <c r="CK132" s="4">
         <v>0</v>
       </c>
       <c r="CL132" s="4">
@@ -60549,10 +60549,10 @@
         <v>0</v>
       </c>
       <c r="CT132" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CU132" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CV132" s="4">
         <v>0</v>
@@ -60581,8 +60581,8 @@
       <c r="DD132" s="4">
         <v>0</v>
       </c>
-      <c r="DE132" s="4">
-        <v>0</v>
+      <c r="DE132">
+        <v>13</v>
       </c>
       <c r="DF132">
         <v>13</v>
@@ -60973,8 +60973,8 @@
       <c r="CJ133">
         <v>13</v>
       </c>
-      <c r="CK133">
-        <v>13</v>
+      <c r="CK133" s="4">
+        <v>0</v>
       </c>
       <c r="CL133" s="4">
         <v>0</v>
@@ -61033,8 +61033,8 @@
       <c r="DD133" s="4">
         <v>0</v>
       </c>
-      <c r="DE133" s="4">
-        <v>0</v>
+      <c r="DE133">
+        <v>13</v>
       </c>
       <c r="DF133">
         <v>13</v>
@@ -61425,8 +61425,8 @@
       <c r="CJ134">
         <v>13</v>
       </c>
-      <c r="CK134">
-        <v>13</v>
+      <c r="CK134" s="4">
+        <v>0</v>
       </c>
       <c r="CL134" s="4">
         <v>0</v>
@@ -61485,8 +61485,8 @@
       <c r="DD134" s="4">
         <v>0</v>
       </c>
-      <c r="DE134" s="4">
-        <v>0</v>
+      <c r="DE134">
+        <v>13</v>
       </c>
       <c r="DF134">
         <v>13</v>
@@ -61877,8 +61877,8 @@
       <c r="CJ135">
         <v>13</v>
       </c>
-      <c r="CK135">
-        <v>13</v>
+      <c r="CK135" s="4">
+        <v>0</v>
       </c>
       <c r="CL135" s="4">
         <v>0</v>
@@ -61937,8 +61937,8 @@
       <c r="DD135" s="4">
         <v>0</v>
       </c>
-      <c r="DE135" s="4">
-        <v>0</v>
+      <c r="DE135">
+        <v>13</v>
       </c>
       <c r="DF135">
         <v>13</v>
@@ -62329,8 +62329,8 @@
       <c r="CJ136">
         <v>13</v>
       </c>
-      <c r="CK136">
-        <v>13</v>
+      <c r="CK136" s="4">
+        <v>0</v>
       </c>
       <c r="CL136" s="4">
         <v>0</v>
@@ -62389,8 +62389,8 @@
       <c r="DD136" s="4">
         <v>0</v>
       </c>
-      <c r="DE136" s="4">
-        <v>0</v>
+      <c r="DE136">
+        <v>13</v>
       </c>
       <c r="DF136">
         <v>13</v>
@@ -62781,8 +62781,8 @@
       <c r="CJ137">
         <v>13</v>
       </c>
-      <c r="CK137">
-        <v>13</v>
+      <c r="CK137" s="4">
+        <v>0</v>
       </c>
       <c r="CL137" s="4">
         <v>0</v>
@@ -62841,8 +62841,8 @@
       <c r="DD137" s="4">
         <v>0</v>
       </c>
-      <c r="DE137" s="4">
-        <v>0</v>
+      <c r="DE137">
+        <v>13</v>
       </c>
       <c r="DF137">
         <v>13</v>
@@ -63233,8 +63233,8 @@
       <c r="CJ138">
         <v>13</v>
       </c>
-      <c r="CK138">
-        <v>13</v>
+      <c r="CK138" s="4">
+        <v>0</v>
       </c>
       <c r="CL138" s="4">
         <v>0</v>
@@ -63293,8 +63293,8 @@
       <c r="DD138" s="4">
         <v>0</v>
       </c>
-      <c r="DE138" s="4">
-        <v>0</v>
+      <c r="DE138">
+        <v>13</v>
       </c>
       <c r="DF138">
         <v>13</v>
@@ -63685,8 +63685,8 @@
       <c r="CJ139">
         <v>13</v>
       </c>
-      <c r="CK139">
-        <v>13</v>
+      <c r="CK139" s="4">
+        <v>0</v>
       </c>
       <c r="CL139" s="4">
         <v>0</v>
@@ -63745,8 +63745,8 @@
       <c r="DD139" s="4">
         <v>0</v>
       </c>
-      <c r="DE139" s="4">
-        <v>0</v>
+      <c r="DE139">
+        <v>13</v>
       </c>
       <c r="DF139">
         <v>13</v>
@@ -64137,6 +64137,9 @@
       <c r="CJ140">
         <v>13</v>
       </c>
+      <c r="CK140" s="4">
+        <v>0</v>
+      </c>
       <c r="CL140" s="4">
         <v>0</v>
       </c>
@@ -64194,8 +64197,8 @@
       <c r="DD140" s="4">
         <v>0</v>
       </c>
-      <c r="DE140" s="4">
-        <v>0</v>
+      <c r="DE140">
+        <v>13</v>
       </c>
       <c r="DF140">
         <v>13</v>
@@ -64586,6 +64589,9 @@
       <c r="CJ141">
         <v>13</v>
       </c>
+      <c r="CK141" s="4">
+        <v>0</v>
+      </c>
       <c r="CL141" s="4">
         <v>0</v>
       </c>
@@ -64643,8 +64649,8 @@
       <c r="DD141" s="4">
         <v>0</v>
       </c>
-      <c r="DE141" s="4">
-        <v>0</v>
+      <c r="DE141">
+        <v>13</v>
       </c>
       <c r="DF141">
         <v>13</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67A07B2-E1BD-4B01-867C-DAB4D94904E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD9A27BA-4250-4232-8008-8B44DA4C1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +397,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,7 +651,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -662,6 +668,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -29740,20 +29749,20 @@
       <c r="BU64">
         <v>13</v>
       </c>
-      <c r="BV64">
-        <v>13</v>
-      </c>
-      <c r="BW64">
-        <v>13</v>
-      </c>
-      <c r="BX64">
-        <v>13</v>
-      </c>
-      <c r="BY64">
-        <v>13</v>
-      </c>
-      <c r="BZ64">
-        <v>13</v>
+      <c r="BV64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BW64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BX64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY64" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ64" s="6">
+        <v>12</v>
       </c>
       <c r="CA64">
         <v>13</v>
@@ -39232,20 +39241,20 @@
       <c r="BU85">
         <v>13</v>
       </c>
-      <c r="BV85">
-        <v>13</v>
-      </c>
-      <c r="BW85">
-        <v>13</v>
-      </c>
-      <c r="BX85">
-        <v>13</v>
-      </c>
-      <c r="BY85">
-        <v>13</v>
-      </c>
-      <c r="BZ85">
-        <v>13</v>
+      <c r="BV85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BW85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BX85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BY85" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ85" s="6">
+        <v>12</v>
       </c>
       <c r="CA85">
         <v>13</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD9A27BA-4250-4232-8008-8B44DA4C1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0367291-7F40-4B2E-9B5B-98E49EB8561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -29749,20 +29749,20 @@
       <c r="BU64">
         <v>13</v>
       </c>
-      <c r="BV64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BW64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BX64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY64" s="6">
-        <v>12</v>
-      </c>
-      <c r="BZ64" s="6">
-        <v>12</v>
+      <c r="BV64">
+        <v>13</v>
+      </c>
+      <c r="BW64">
+        <v>13</v>
+      </c>
+      <c r="BX64">
+        <v>13</v>
+      </c>
+      <c r="BY64">
+        <v>13</v>
+      </c>
+      <c r="BZ64">
+        <v>13</v>
       </c>
       <c r="CA64">
         <v>13</v>
@@ -30195,37 +30195,37 @@
       <c r="BS65" s="4">
         <v>0</v>
       </c>
-      <c r="BT65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY65" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ65" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA65" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB65" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC65" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD65" s="4">
+      <c r="BT65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BX65" s="6">
+        <v>0</v>
+      </c>
+      <c r="BY65" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC65" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD65" s="6">
         <v>0</v>
       </c>
       <c r="CE65" s="4">
@@ -34279,7 +34279,7 @@
         <v>0</v>
       </c>
       <c r="BY74" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BZ74" s="4">
         <v>0</v>
@@ -34728,7 +34728,7 @@
         <v>0</v>
       </c>
       <c r="BX75" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BY75" s="4">
         <v>0</v>
@@ -38783,37 +38783,37 @@
       <c r="BS84" s="4">
         <v>0</v>
       </c>
-      <c r="BT84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BV84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BW84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BY84" s="4">
-        <v>0</v>
-      </c>
-      <c r="BZ84" s="4">
-        <v>0</v>
-      </c>
-      <c r="CA84" s="4">
-        <v>0</v>
-      </c>
-      <c r="CB84" s="4">
-        <v>0</v>
-      </c>
-      <c r="CC84" s="4">
-        <v>0</v>
-      </c>
-      <c r="CD84" s="4">
+      <c r="BT84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BX84" s="6">
+        <v>0</v>
+      </c>
+      <c r="BY84" s="6">
+        <v>12</v>
+      </c>
+      <c r="BZ84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC84" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD84" s="6">
         <v>0</v>
       </c>
       <c r="CE84" s="4">
@@ -39241,20 +39241,20 @@
       <c r="BU85">
         <v>13</v>
       </c>
-      <c r="BV85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BW85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BX85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY85" s="6">
-        <v>12</v>
-      </c>
-      <c r="BZ85" s="6">
-        <v>12</v>
+      <c r="BV85">
+        <v>13</v>
+      </c>
+      <c r="BW85">
+        <v>13</v>
+      </c>
+      <c r="BX85">
+        <v>13</v>
+      </c>
+      <c r="BY85">
+        <v>13</v>
+      </c>
+      <c r="BZ85">
+        <v>13</v>
       </c>
       <c r="CA85">
         <v>13</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0367291-7F40-4B2E-9B5B-98E49EB8561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC01F261-1A84-453E-B91F-F0FE955ED1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1" s="1">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="K1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="1">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1" s="1">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="Q1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1" s="1">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="T1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U1" s="1">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="W1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X1" s="1">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="Z1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA1" s="1">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="AC1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD1" s="1">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="AF1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG1" s="1">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="AI1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ1" s="1">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="AL1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM1" s="1">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="AO1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP1" s="1">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="AR1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS1" s="1">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="AU1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV1" s="1">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="AX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY1" s="1">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="BA1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB1" s="1">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="BD1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE1" s="1">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="BG1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH1" s="1">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="BJ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK1" s="1">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="BM1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN1" s="1">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="BP1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ1" s="1">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="BS1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT1" s="1">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="BV1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW1" s="1">
         <v>0</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="BY1" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="BZ1" s="1">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="CB1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC1" s="1">
         <v>0</v>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="CE1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF1" s="1">
         <v>0</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="CH1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI1" s="1">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="CK1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL1" s="1">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="CN1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO1" s="1">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="CQ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR1" s="1">
         <v>0</v>
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="CT1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU1" s="1">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="CW1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX1" s="1">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="CZ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA1" s="1">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="DC1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD1" s="1">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="DF1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG1" s="1">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="DI1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ1" s="1">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="DL1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM1" s="1">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="DO1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP1" s="1">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="DR1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS1" s="1">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="DU1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV1" s="1">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="DX1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY1" s="1">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="EA1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB1" s="1">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="ED1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE1" s="1">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="EG1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH1" s="1">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="EJ1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK1" s="1">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="EM1" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN1" s="1">
         <v>0</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="8" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>13</v>
@@ -4669,7 +4669,7 @@
         <v>13</v>
       </c>
       <c r="ET8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:150" x14ac:dyDescent="0.45">
@@ -5578,7 +5578,7 @@
     </row>
     <row r="11" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>13</v>
@@ -6025,7 +6025,7 @@
         <v>13</v>
       </c>
       <c r="ET11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:150" x14ac:dyDescent="0.45">
@@ -6934,7 +6934,7 @@
     </row>
     <row r="14" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -7381,7 +7381,7 @@
         <v>13</v>
       </c>
       <c r="ET14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:150" x14ac:dyDescent="0.45">
@@ -8290,7 +8290,7 @@
     </row>
     <row r="17" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B17">
         <v>13</v>
@@ -8737,7 +8737,7 @@
         <v>13</v>
       </c>
       <c r="ET17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:150" x14ac:dyDescent="0.45">
@@ -9646,7 +9646,7 @@
     </row>
     <row r="20" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20">
         <v>13</v>
@@ -10093,7 +10093,7 @@
         <v>13</v>
       </c>
       <c r="ET20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:150" x14ac:dyDescent="0.45">
@@ -11002,7 +11002,7 @@
     </row>
     <row r="23" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B23">
         <v>13</v>
@@ -11449,7 +11449,7 @@
         <v>13</v>
       </c>
       <c r="ET23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:150" x14ac:dyDescent="0.45">
@@ -12358,7 +12358,7 @@
     </row>
     <row r="26" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B26">
         <v>13</v>
@@ -12805,7 +12805,7 @@
         <v>13</v>
       </c>
       <c r="ET26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:150" x14ac:dyDescent="0.45">
@@ -13714,7 +13714,7 @@
     </row>
     <row r="29" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B29">
         <v>13</v>
@@ -14161,7 +14161,7 @@
         <v>13</v>
       </c>
       <c r="ET29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:150" x14ac:dyDescent="0.45">
@@ -15070,7 +15070,7 @@
     </row>
     <row r="32" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B32">
         <v>13</v>
@@ -15517,7 +15517,7 @@
         <v>13</v>
       </c>
       <c r="ET32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:150" x14ac:dyDescent="0.45">
@@ -16426,7 +16426,7 @@
     </row>
     <row r="35" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B35">
         <v>13</v>
@@ -16873,7 +16873,7 @@
         <v>13</v>
       </c>
       <c r="ET35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:150" x14ac:dyDescent="0.45">
@@ -17782,7 +17782,7 @@
     </row>
     <row r="38" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38">
         <v>13</v>
@@ -18229,7 +18229,7 @@
         <v>13</v>
       </c>
       <c r="ET38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:150" x14ac:dyDescent="0.45">
@@ -19138,7 +19138,7 @@
     </row>
     <row r="41" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B41">
         <v>13</v>
@@ -19585,7 +19585,7 @@
         <v>13</v>
       </c>
       <c r="ET41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:150" x14ac:dyDescent="0.45">
@@ -20494,7 +20494,7 @@
     </row>
     <row r="44" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -20938,7 +20938,7 @@
         <v>13</v>
       </c>
       <c r="ET44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:150" x14ac:dyDescent="0.45">
@@ -21847,7 +21847,7 @@
     </row>
     <row r="47" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B47">
         <v>13</v>
@@ -22294,7 +22294,7 @@
         <v>13</v>
       </c>
       <c r="ET47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:150" x14ac:dyDescent="0.45">
@@ -23203,7 +23203,7 @@
     </row>
     <row r="50" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B50">
         <v>13</v>
@@ -23650,7 +23650,7 @@
         <v>13</v>
       </c>
       <c r="ET50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:150" x14ac:dyDescent="0.45">
@@ -24559,7 +24559,7 @@
     </row>
     <row r="53" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B53">
         <v>13</v>
@@ -25006,7 +25006,7 @@
         <v>13</v>
       </c>
       <c r="ET53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:150" x14ac:dyDescent="0.45">
@@ -25915,7 +25915,7 @@
     </row>
     <row r="56" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56">
         <v>13</v>
@@ -26362,7 +26362,7 @@
         <v>13</v>
       </c>
       <c r="ET56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:150" x14ac:dyDescent="0.45">
@@ -27271,7 +27271,7 @@
     </row>
     <row r="59" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B59">
         <v>13</v>
@@ -27718,7 +27718,7 @@
         <v>13</v>
       </c>
       <c r="ET59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:150" x14ac:dyDescent="0.45">
@@ -28627,7 +28627,7 @@
     </row>
     <row r="62" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B62">
         <v>13</v>
@@ -29074,7 +29074,7 @@
         <v>13</v>
       </c>
       <c r="ET62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:150" x14ac:dyDescent="0.45">
@@ -29983,7 +29983,7 @@
     </row>
     <row r="65" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B65">
         <v>13</v>
@@ -30430,7 +30430,7 @@
         <v>13</v>
       </c>
       <c r="ET65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:150" x14ac:dyDescent="0.45">
@@ -31339,7 +31339,7 @@
     </row>
     <row r="68" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B68">
         <v>13</v>
@@ -31786,7 +31786,7 @@
         <v>13</v>
       </c>
       <c r="ET68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:150" x14ac:dyDescent="0.45">
@@ -32695,7 +32695,7 @@
     </row>
     <row r="71" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B71">
         <v>13</v>
@@ -33142,7 +33142,7 @@
         <v>13</v>
       </c>
       <c r="ET71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:150" x14ac:dyDescent="0.45">
@@ -34051,7 +34051,7 @@
     </row>
     <row r="74" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B74" s="1">
         <v>0</v>
@@ -34498,7 +34498,7 @@
         <v>0</v>
       </c>
       <c r="ET74" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:150" x14ac:dyDescent="0.45">
@@ -35407,7 +35407,7 @@
     </row>
     <row r="77" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B77">
         <v>13</v>
@@ -35854,7 +35854,7 @@
         <v>13</v>
       </c>
       <c r="ET77" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:150" x14ac:dyDescent="0.45">
@@ -36763,7 +36763,7 @@
     </row>
     <row r="80" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B80">
         <v>13</v>
@@ -37210,7 +37210,7 @@
         <v>13</v>
       </c>
       <c r="ET80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:150" x14ac:dyDescent="0.45">
@@ -38119,7 +38119,7 @@
     </row>
     <row r="83" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B83">
         <v>13</v>
@@ -38566,7 +38566,7 @@
         <v>13</v>
       </c>
       <c r="ET83" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:150" x14ac:dyDescent="0.45">
@@ -39475,7 +39475,7 @@
     </row>
     <row r="86" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B86">
         <v>13</v>
@@ -39922,7 +39922,7 @@
         <v>13</v>
       </c>
       <c r="ET86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:150" x14ac:dyDescent="0.45">
@@ -40831,7 +40831,7 @@
     </row>
     <row r="89" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B89">
         <v>13</v>
@@ -41278,7 +41278,7 @@
         <v>13</v>
       </c>
       <c r="ET89" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:150" x14ac:dyDescent="0.45">
@@ -42187,7 +42187,7 @@
     </row>
     <row r="92" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B92">
         <v>13</v>
@@ -42634,7 +42634,7 @@
         <v>13</v>
       </c>
       <c r="ET92" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:150" x14ac:dyDescent="0.45">
@@ -43543,7 +43543,7 @@
     </row>
     <row r="95" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B95">
         <v>13</v>
@@ -43990,7 +43990,7 @@
         <v>13</v>
       </c>
       <c r="ET95" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:150" x14ac:dyDescent="0.45">
@@ -44899,7 +44899,7 @@
     </row>
     <row r="98" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B98">
         <v>13</v>
@@ -45346,7 +45346,7 @@
         <v>13</v>
       </c>
       <c r="ET98" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:150" x14ac:dyDescent="0.45">
@@ -46255,7 +46255,7 @@
     </row>
     <row r="101" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B101">
         <v>13</v>
@@ -46702,7 +46702,7 @@
         <v>13</v>
       </c>
       <c r="ET101" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:150" x14ac:dyDescent="0.45">
@@ -47611,7 +47611,7 @@
     </row>
     <row r="104" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B104">
         <v>13</v>
@@ -48058,7 +48058,7 @@
         <v>13</v>
       </c>
       <c r="ET104" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:150" x14ac:dyDescent="0.45">
@@ -48967,7 +48967,7 @@
     </row>
     <row r="107" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B107">
         <v>13</v>
@@ -49414,7 +49414,7 @@
         <v>13</v>
       </c>
       <c r="ET107" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:150" x14ac:dyDescent="0.45">
@@ -50323,7 +50323,7 @@
     </row>
     <row r="110" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B110">
         <v>13</v>
@@ -50770,7 +50770,7 @@
         <v>13</v>
       </c>
       <c r="ET110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:150" x14ac:dyDescent="0.45">
@@ -51679,7 +51679,7 @@
     </row>
     <row r="113" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B113">
         <v>13</v>
@@ -52126,7 +52126,7 @@
         <v>13</v>
       </c>
       <c r="ET113" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:150" x14ac:dyDescent="0.45">
@@ -53035,7 +53035,7 @@
     </row>
     <row r="116" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B116">
         <v>13</v>
@@ -53482,7 +53482,7 @@
         <v>13</v>
       </c>
       <c r="ET116" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:150" x14ac:dyDescent="0.45">
@@ -54391,7 +54391,7 @@
     </row>
     <row r="119" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B119">
         <v>13</v>
@@ -54838,7 +54838,7 @@
         <v>13</v>
       </c>
       <c r="ET119" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:150" x14ac:dyDescent="0.45">
@@ -55747,7 +55747,7 @@
     </row>
     <row r="122" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B122">
         <v>13</v>
@@ -56194,7 +56194,7 @@
         <v>13</v>
       </c>
       <c r="ET122" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:150" x14ac:dyDescent="0.45">
@@ -57103,7 +57103,7 @@
     </row>
     <row r="125" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B125">
         <v>13</v>
@@ -57550,7 +57550,7 @@
         <v>13</v>
       </c>
       <c r="ET125" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:150" x14ac:dyDescent="0.45">
@@ -58459,7 +58459,7 @@
     </row>
     <row r="128" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B128">
         <v>13</v>
@@ -58906,7 +58906,7 @@
         <v>13</v>
       </c>
       <c r="ET128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:150" x14ac:dyDescent="0.45">
@@ -59815,7 +59815,7 @@
     </row>
     <row r="131" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B131">
         <v>13</v>
@@ -60262,7 +60262,7 @@
         <v>13</v>
       </c>
       <c r="ET131" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:150" x14ac:dyDescent="0.45">
@@ -61171,7 +61171,7 @@
     </row>
     <row r="134" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B134">
         <v>13</v>
@@ -61618,7 +61618,7 @@
         <v>13</v>
       </c>
       <c r="ET134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:150" x14ac:dyDescent="0.45">
@@ -62527,7 +62527,7 @@
     </row>
     <row r="137" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B137">
         <v>13</v>
@@ -62974,7 +62974,7 @@
         <v>13</v>
       </c>
       <c r="ET137" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:150" x14ac:dyDescent="0.45">
@@ -63883,7 +63883,7 @@
     </row>
     <row r="140" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B140">
         <v>13</v>
@@ -64330,7 +64330,7 @@
         <v>13</v>
       </c>
       <c r="ET140" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:150" x14ac:dyDescent="0.45">
@@ -65239,7 +65239,7 @@
     </row>
     <row r="143" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B143">
         <v>13</v>
@@ -65686,7 +65686,7 @@
         <v>13</v>
       </c>
       <c r="ET143" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:150" x14ac:dyDescent="0.45">
@@ -68424,7 +68424,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
@@ -68433,7 +68433,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="1">
         <v>0</v>
@@ -68442,7 +68442,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" s="1">
         <v>0</v>
@@ -68451,7 +68451,7 @@
         <v>0</v>
       </c>
       <c r="Q150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R150" s="1">
         <v>0</v>
@@ -68460,7 +68460,7 @@
         <v>0</v>
       </c>
       <c r="T150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U150" s="1">
         <v>0</v>
@@ -68469,7 +68469,7 @@
         <v>0</v>
       </c>
       <c r="W150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X150" s="1">
         <v>0</v>
@@ -68478,7 +68478,7 @@
         <v>0</v>
       </c>
       <c r="Z150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA150" s="1">
         <v>0</v>
@@ -68487,7 +68487,7 @@
         <v>0</v>
       </c>
       <c r="AC150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD150" s="1">
         <v>0</v>
@@ -68496,7 +68496,7 @@
         <v>0</v>
       </c>
       <c r="AF150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG150" s="1">
         <v>0</v>
@@ -68505,7 +68505,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ150" s="1">
         <v>0</v>
@@ -68514,7 +68514,7 @@
         <v>0</v>
       </c>
       <c r="AL150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM150" s="1">
         <v>0</v>
@@ -68523,7 +68523,7 @@
         <v>0</v>
       </c>
       <c r="AO150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP150" s="1">
         <v>0</v>
@@ -68532,7 +68532,7 @@
         <v>0</v>
       </c>
       <c r="AR150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS150" s="1">
         <v>0</v>
@@ -68541,7 +68541,7 @@
         <v>0</v>
       </c>
       <c r="AU150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV150" s="1">
         <v>0</v>
@@ -68550,7 +68550,7 @@
         <v>0</v>
       </c>
       <c r="AX150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY150" s="1">
         <v>0</v>
@@ -68559,7 +68559,7 @@
         <v>0</v>
       </c>
       <c r="BA150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB150" s="1">
         <v>0</v>
@@ -68568,7 +68568,7 @@
         <v>0</v>
       </c>
       <c r="BD150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE150" s="1">
         <v>0</v>
@@ -68577,7 +68577,7 @@
         <v>0</v>
       </c>
       <c r="BG150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH150" s="1">
         <v>0</v>
@@ -68586,7 +68586,7 @@
         <v>0</v>
       </c>
       <c r="BJ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK150" s="1">
         <v>0</v>
@@ -68595,7 +68595,7 @@
         <v>0</v>
       </c>
       <c r="BM150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN150" s="1">
         <v>0</v>
@@ -68604,7 +68604,7 @@
         <v>0</v>
       </c>
       <c r="BP150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ150" s="1">
         <v>0</v>
@@ -68613,7 +68613,7 @@
         <v>0</v>
       </c>
       <c r="BS150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT150" s="1">
         <v>0</v>
@@ -68622,7 +68622,7 @@
         <v>0</v>
       </c>
       <c r="BV150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW150" s="1">
         <v>0</v>
@@ -68631,7 +68631,7 @@
         <v>0</v>
       </c>
       <c r="BY150" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="BZ150" s="1">
         <v>0</v>
@@ -68640,7 +68640,7 @@
         <v>0</v>
       </c>
       <c r="CB150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC150" s="1">
         <v>0</v>
@@ -68649,7 +68649,7 @@
         <v>0</v>
       </c>
       <c r="CE150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF150" s="1">
         <v>0</v>
@@ -68658,7 +68658,7 @@
         <v>0</v>
       </c>
       <c r="CH150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI150" s="1">
         <v>0</v>
@@ -68667,7 +68667,7 @@
         <v>0</v>
       </c>
       <c r="CK150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL150" s="1">
         <v>0</v>
@@ -68676,7 +68676,7 @@
         <v>0</v>
       </c>
       <c r="CN150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO150" s="1">
         <v>0</v>
@@ -68685,7 +68685,7 @@
         <v>0</v>
       </c>
       <c r="CQ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR150" s="1">
         <v>0</v>
@@ -68694,7 +68694,7 @@
         <v>0</v>
       </c>
       <c r="CT150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU150" s="1">
         <v>0</v>
@@ -68703,7 +68703,7 @@
         <v>0</v>
       </c>
       <c r="CW150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX150" s="1">
         <v>0</v>
@@ -68712,7 +68712,7 @@
         <v>0</v>
       </c>
       <c r="CZ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA150" s="1">
         <v>0</v>
@@ -68721,7 +68721,7 @@
         <v>0</v>
       </c>
       <c r="DC150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD150" s="1">
         <v>0</v>
@@ -68730,7 +68730,7 @@
         <v>0</v>
       </c>
       <c r="DF150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG150" s="1">
         <v>0</v>
@@ -68739,7 +68739,7 @@
         <v>0</v>
       </c>
       <c r="DI150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ150" s="1">
         <v>0</v>
@@ -68748,7 +68748,7 @@
         <v>0</v>
       </c>
       <c r="DL150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM150" s="1">
         <v>0</v>
@@ -68757,7 +68757,7 @@
         <v>0</v>
       </c>
       <c r="DO150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP150" s="1">
         <v>0</v>
@@ -68766,7 +68766,7 @@
         <v>0</v>
       </c>
       <c r="DR150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS150" s="1">
         <v>0</v>
@@ -68775,7 +68775,7 @@
         <v>0</v>
       </c>
       <c r="DU150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV150" s="1">
         <v>0</v>
@@ -68784,7 +68784,7 @@
         <v>0</v>
       </c>
       <c r="DX150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY150" s="1">
         <v>0</v>
@@ -68793,7 +68793,7 @@
         <v>0</v>
       </c>
       <c r="EA150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB150" s="1">
         <v>0</v>
@@ -68802,7 +68802,7 @@
         <v>0</v>
       </c>
       <c r="ED150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE150" s="1">
         <v>0</v>
@@ -68811,7 +68811,7 @@
         <v>0</v>
       </c>
       <c r="EG150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH150" s="1">
         <v>0</v>
@@ -68820,7 +68820,7 @@
         <v>0</v>
       </c>
       <c r="EJ150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK150" s="1">
         <v>0</v>
@@ -68829,7 +68829,7 @@
         <v>0</v>
       </c>
       <c r="EM150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN150" s="1">
         <v>0</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20CECDB-3DC6-46C8-AD58-E8A05644852E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52995564-FA2D-4DBE-BF9D-A353E96B7C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1908" yWindow="408" windowWidth="13836" windowHeight="11712" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="Y17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV17" s="1">
         <v>0</v>
@@ -1564,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="Y20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV20" s="1">
         <v>0</v>
@@ -1578,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="1">
         <v>0</v>
@@ -1624,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV23" s="1">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="Q24" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="Y26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV26" s="1">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="Q27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI29" s="1">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="BO29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CC29" s="3">
         <v>0</v>
@@ -1911,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q30" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
@@ -2083,16 +2083,16 @@
         <v>0</v>
       </c>
       <c r="Y32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX32" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CC32" s="3">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>0</v>
       </c>
       <c r="Y35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX35" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV35" s="1">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="Y38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF38" s="3">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="BX38" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV38" s="1">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Y41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF41" s="3">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="BX41" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA41" s="2">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="AH43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO43" s="2">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="BO43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX43" s="1">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="Y44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH44" s="1">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="BX44" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA44" s="2">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="AH46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO46" s="2">
         <v>0</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="BO46" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA46" s="2">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="AH49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO49" s="2">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="BO49" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA49" s="2">
         <v>0</v>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="AH52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO52" s="2">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="BO52" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA52" s="2">
         <v>0</v>
@@ -5169,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="Y54" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH54" s="1">
         <v>0</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="BX54" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA54" s="2">
         <v>0</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="AH55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO55" s="2">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="BO55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX55" s="1">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="Y57" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
@@ -5862,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="BX57" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CA57" s="2">
         <v>0</v>
@@ -6441,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF60" s="3">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="BX60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV60" s="1">
         <v>0</v>
@@ -6669,16 +6669,16 @@
         <v>0</v>
       </c>
       <c r="Y63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV63" s="1">
         <v>0</v>
@@ -6759,16 +6759,16 @@
         <v>0</v>
       </c>
       <c r="Y66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD66" s="3">
         <v>0</v>
@@ -6957,16 +6957,16 @@
         <v>0</v>
       </c>
       <c r="Y69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD69" s="3">
         <v>0</v>
@@ -7135,10 +7135,10 @@
         <v>0</v>
       </c>
       <c r="CF71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ71" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV71" s="1">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="Y72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI72" s="1">
         <v>0</v>
@@ -7236,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="BO72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX72" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF72" s="1">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>8</v>
       </c>
       <c r="CQ74" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV74" s="1">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="Y75" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX75" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF75" s="4">
         <v>0</v>
@@ -7411,7 +7411,7 @@
         <v>8</v>
       </c>
       <c r="CQ77" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV77" s="1">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="Y78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF78" s="4">
         <v>0</v>
@@ -7468,10 +7468,10 @@
         <v>0</v>
       </c>
       <c r="CF80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CQ80" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CV80" s="1">
         <v>0</v>
@@ -7482,10 +7482,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX81" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CF81" s="1">
         <v>0</v>
@@ -7590,10 +7590,10 @@
         <v>0</v>
       </c>
       <c r="Y84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BX84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CD84" s="3">
         <v>0</v>

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52995564-FA2D-4DBE-BF9D-A353E96B7C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD96424-AFD9-45C8-939F-12882C11B0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="84" windowWidth="13836" windowHeight="12156" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="228" yWindow="144" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1250,6 +1250,12 @@
       <c r="A15" s="1">
         <v>0</v>
       </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
@@ -1259,10 +1265,10 @@
       <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
@@ -1272,12 +1278,6 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3">
         <v>0</v>
       </c>
       <c r="W15" s="3">
@@ -1363,6 +1363,12 @@
       <c r="A16" s="1">
         <v>0</v>
       </c>
+      <c r="B16" s="3">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
@@ -1372,10 +1378,10 @@
       <c r="F16" s="3">
         <v>0</v>
       </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
         <v>0</v>
       </c>
       <c r="O16" s="3">
@@ -1385,12 +1391,6 @@
         <v>0</v>
       </c>
       <c r="Q16" s="3">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3">
         <v>0</v>
       </c>
       <c r="Y16" s="1">
@@ -1407,52 +1407,52 @@
       <c r="A17" s="1">
         <v>0</v>
       </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>11</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>3</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>3</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
       <c r="Q17" s="3">
-        <v>11</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
         <v>0</v>
       </c>
       <c r="Y17" s="1">
@@ -1469,6 +1469,12 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
+      <c r="B18" s="3">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
       <c r="D18" s="3">
         <v>0</v>
       </c>
@@ -1478,10 +1484,10 @@
       <c r="F18" s="3">
         <v>0</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>0</v>
       </c>
       <c r="O18" s="3">
@@ -1491,12 +1497,6 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
         <v>0</v>
       </c>
       <c r="Y18" s="1">
@@ -1513,6 +1513,12 @@
       <c r="A19" s="1">
         <v>0</v>
       </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
       <c r="D19" s="3">
         <v>0</v>
       </c>
@@ -1522,10 +1528,10 @@
       <c r="F19" s="3">
         <v>0</v>
       </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
         <v>0</v>
       </c>
       <c r="O19" s="3">
@@ -1535,12 +1541,6 @@
         <v>0</v>
       </c>
       <c r="Q19" s="3">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0</v>
-      </c>
-      <c r="S19" s="3">
         <v>0</v>
       </c>
       <c r="Y19" s="1">
@@ -1557,10 +1557,7 @@
       <c r="A20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
+      <c r="P20" s="1">
         <v>0</v>
       </c>
       <c r="Y20" s="1">
@@ -1577,10 +1574,7 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="1">
+      <c r="P21" s="1">
         <v>4</v>
       </c>
       <c r="Y21" s="1">
@@ -1597,10 +1591,7 @@
       <c r="A22" s="1">
         <v>0</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
+      <c r="P22" s="1">
         <v>0</v>
       </c>
       <c r="Y22" s="1">
@@ -1617,10 +1608,7 @@
       <c r="A23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
+      <c r="P23" s="4">
         <v>0</v>
       </c>
       <c r="Y23" s="1">
@@ -1637,11 +1625,8 @@
       <c r="A24" s="1">
         <v>0</v>
       </c>
-      <c r="F24" s="4">
+      <c r="P24" s="4">
         <v>8</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>4</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -1657,10 +1642,7 @@
       <c r="A25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
+      <c r="P25" s="4">
         <v>0</v>
       </c>
       <c r="Y25" s="1">
@@ -1677,10 +1659,7 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
+      <c r="P26" s="4">
         <v>0</v>
       </c>
       <c r="Y26" s="1">
@@ -1697,15 +1676,15 @@
       <c r="A27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="4">
+      <c r="P27" s="4">
         <v>8</v>
       </c>
-      <c r="Q27" s="1">
-        <v>4</v>
-      </c>
       <c r="Y27" s="1">
         <v>0</v>
       </c>
+      <c r="AN27" s="3">
+        <v>0</v>
+      </c>
       <c r="AO27" s="3">
         <v>0</v>
       </c>
@@ -1718,12 +1697,6 @@
       <c r="AR27" s="3">
         <v>0</v>
       </c>
-      <c r="AS27" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD27" s="3">
-        <v>0</v>
-      </c>
       <c r="BE27" s="3">
         <v>0</v>
       </c>
@@ -1734,6 +1707,9 @@
         <v>0</v>
       </c>
       <c r="BH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3">
         <v>0</v>
       </c>
       <c r="BX27" s="1">
@@ -1747,16 +1723,16 @@
       <c r="A28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="1">
+      <c r="P28" s="4">
         <v>0</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
       </c>
-      <c r="AH28" s="1">
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
         <v>0</v>
       </c>
       <c r="AO28" s="3">
@@ -1771,12 +1747,6 @@
       <c r="AR28" s="3">
         <v>0</v>
       </c>
-      <c r="AS28" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD28" s="3">
-        <v>0</v>
-      </c>
       <c r="BE28" s="3">
         <v>0</v>
       </c>
@@ -1789,7 +1759,10 @@
       <c r="BH28" s="3">
         <v>0</v>
       </c>
-      <c r="BO28" s="1">
+      <c r="BI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP28" s="1">
         <v>0</v>
       </c>
       <c r="BX28" s="1">
@@ -1803,85 +1776,82 @@
       <c r="A29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1">
+      <c r="P29" s="1">
         <v>0</v>
       </c>
       <c r="Y29" s="1">
         <v>4</v>
       </c>
+      <c r="AG29" s="1">
+        <v>4</v>
+      </c>
       <c r="AH29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="1">
         <v>3</v>
       </c>
-      <c r="AK29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="1">
-        <v>0</v>
-      </c>
       <c r="AM29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>11</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG29" s="3">
+        <v>11</v>
+      </c>
+      <c r="BH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BJ29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK29" s="1">
         <v>3</v>
       </c>
-      <c r="AN29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="3">
-        <v>11</v>
-      </c>
-      <c r="AR29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF29" s="3">
-        <v>11</v>
-      </c>
-      <c r="BG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ29" s="1">
+      <c r="BL29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN29" s="1">
         <v>3</v>
       </c>
-      <c r="BK29" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL29" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM29" s="1">
-        <v>3</v>
-      </c>
-      <c r="BN29" s="1">
-        <v>0</v>
-      </c>
       <c r="BO29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP29" s="1">
         <v>4</v>
       </c>
       <c r="BX29" s="1">
@@ -1910,16 +1880,16 @@
       <c r="A30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1">
-        <v>4</v>
-      </c>
-      <c r="Q30" s="1">
+      <c r="P30" s="1">
         <v>4</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
       </c>
-      <c r="AH30" s="1">
+      <c r="AG30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
         <v>0</v>
       </c>
       <c r="AO30" s="3">
@@ -1934,12 +1904,6 @@
       <c r="AR30" s="3">
         <v>0</v>
       </c>
-      <c r="AS30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD30" s="3">
-        <v>0</v>
-      </c>
       <c r="BE30" s="3">
         <v>0</v>
       </c>
@@ -1952,7 +1916,10 @@
       <c r="BH30" s="3">
         <v>0</v>
       </c>
-      <c r="BO30" s="1">
+      <c r="BI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP30" s="1">
         <v>0</v>
       </c>
       <c r="BX30" s="1">
@@ -1981,16 +1948,16 @@
       <c r="A31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
+      <c r="P31" s="1">
         <v>0</v>
       </c>
       <c r="Y31" s="1">
         <v>0</v>
       </c>
-      <c r="AH31" s="1">
+      <c r="AG31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
         <v>0</v>
       </c>
       <c r="AO31" s="3">
@@ -2005,12 +1972,6 @@
       <c r="AR31" s="3">
         <v>0</v>
       </c>
-      <c r="AS31" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="3">
-        <v>0</v>
-      </c>
       <c r="BE31" s="3">
         <v>0</v>
       </c>
@@ -2023,7 +1984,10 @@
       <c r="BH31" s="3">
         <v>0</v>
       </c>
-      <c r="BO31" s="1">
+      <c r="BI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP31" s="1">
         <v>0</v>
       </c>
       <c r="BX31" s="1">
@@ -2052,6 +2016,12 @@
       <c r="A32" s="1">
         <v>0</v>
       </c>
+      <c r="B32" s="3">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
@@ -2061,10 +2031,10 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
@@ -2076,19 +2046,13 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="1">
         <v>4</v>
       </c>
-      <c r="AH32" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO32" s="1">
+      <c r="AG32" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP32" s="1">
         <v>4</v>
       </c>
       <c r="BX32" s="1">
@@ -2117,6 +2081,12 @@
       <c r="A33" s="1">
         <v>0</v>
       </c>
+      <c r="B33" s="3">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
       <c r="D33" s="3">
         <v>0</v>
       </c>
@@ -2126,10 +2096,10 @@
       <c r="F33" s="3">
         <v>0</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>0</v>
       </c>
       <c r="O33" s="3">
@@ -2141,19 +2111,13 @@
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="1">
         <v>0</v>
       </c>
-      <c r="AH33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO33" s="1">
+      <c r="AG33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP33" s="1">
         <v>0</v>
       </c>
       <c r="BX33" s="1">
@@ -2182,61 +2146,61 @@
       <c r="A34" s="1">
         <v>0</v>
       </c>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
       <c r="D34" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
         <v>11</v>
       </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>3</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>3</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="3">
-        <v>0</v>
-      </c>
       <c r="P34" s="3">
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <v>11</v>
-      </c>
-      <c r="R34" s="3">
-        <v>0</v>
-      </c>
-      <c r="S34" s="3">
         <v>0</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
       </c>
-      <c r="AH34" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO34" s="1">
+      <c r="AG34" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP34" s="1">
         <v>0</v>
       </c>
       <c r="BX34" s="1">
@@ -2250,6 +2214,12 @@
       <c r="A35" s="1">
         <v>0</v>
       </c>
+      <c r="B35" s="3">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
       <c r="D35" s="3">
         <v>0</v>
       </c>
@@ -2259,10 +2229,10 @@
       <c r="F35" s="3">
         <v>0</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>0</v>
       </c>
       <c r="O35" s="3">
@@ -2274,19 +2244,13 @@
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="1">
         <v>4</v>
       </c>
-      <c r="AH35" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO35" s="1">
+      <c r="AG35" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP35" s="1">
         <v>4</v>
       </c>
       <c r="BX35" s="1">
@@ -2300,6 +2264,12 @@
       <c r="A36" s="1">
         <v>0</v>
       </c>
+      <c r="B36" s="3">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
       <c r="D36" s="3">
         <v>0</v>
       </c>
@@ -2309,10 +2279,10 @@
       <c r="F36" s="3">
         <v>0</v>
       </c>
-      <c r="G36" s="3">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3">
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3">
         <v>0</v>
       </c>
       <c r="O36" s="3">
@@ -2324,19 +2294,13 @@
       <c r="Q36" s="3">
         <v>0</v>
       </c>
-      <c r="R36" s="3">
-        <v>0</v>
-      </c>
-      <c r="S36" s="3">
-        <v>0</v>
-      </c>
       <c r="Y36" s="1">
         <v>0</v>
       </c>
-      <c r="AH36" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO36" s="1">
+      <c r="AG36" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP36" s="1">
         <v>0</v>
       </c>
       <c r="BX36" s="1">
@@ -2353,6 +2317,9 @@
       <c r="Y37" s="1">
         <v>0</v>
       </c>
+      <c r="AE37" s="3">
+        <v>0</v>
+      </c>
       <c r="AF37" s="3">
         <v>0</v>
       </c>
@@ -2365,12 +2332,6 @@
       <c r="AI37" s="3">
         <v>0</v>
       </c>
-      <c r="AJ37" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM37" s="3">
-        <v>0</v>
-      </c>
       <c r="BN37" s="3">
         <v>0</v>
       </c>
@@ -2381,6 +2342,9 @@
         <v>0</v>
       </c>
       <c r="BQ37" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR37" s="3">
         <v>0</v>
       </c>
       <c r="BX37" s="1">
@@ -2397,6 +2361,9 @@
       <c r="Y38" s="1">
         <v>4</v>
       </c>
+      <c r="AE38" s="3">
+        <v>0</v>
+      </c>
       <c r="AF38" s="3">
         <v>0</v>
       </c>
@@ -2409,12 +2376,6 @@
       <c r="AI38" s="3">
         <v>0</v>
       </c>
-      <c r="AJ38" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM38" s="3">
-        <v>0</v>
-      </c>
       <c r="BN38" s="3">
         <v>0</v>
       </c>
@@ -2425,6 +2386,9 @@
         <v>0</v>
       </c>
       <c r="BQ38" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR38" s="3">
         <v>0</v>
       </c>
       <c r="BX38" s="1">
@@ -2441,34 +2405,34 @@
       <c r="Y39" s="1">
         <v>0</v>
       </c>
+      <c r="AE39" s="3">
+        <v>0</v>
+      </c>
       <c r="AF39" s="3">
         <v>0</v>
       </c>
       <c r="AG39" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BN39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP39" s="3">
         <v>11</v>
       </c>
-      <c r="AI39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM39" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN39" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO39" s="3">
-        <v>11</v>
-      </c>
-      <c r="BP39" s="3">
-        <v>0</v>
-      </c>
       <c r="BQ39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR39" s="3">
         <v>0</v>
       </c>
       <c r="BX39" s="1">
@@ -2485,6 +2449,9 @@
       <c r="Y40" s="1">
         <v>0</v>
       </c>
+      <c r="AE40" s="3">
+        <v>0</v>
+      </c>
       <c r="AF40" s="3">
         <v>0</v>
       </c>
@@ -2497,12 +2464,6 @@
       <c r="AI40" s="3">
         <v>0</v>
       </c>
-      <c r="AJ40" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM40" s="3">
-        <v>0</v>
-      </c>
       <c r="BN40" s="3">
         <v>0</v>
       </c>
@@ -2515,67 +2476,10 @@
       <c r="BQ40" s="3">
         <v>0</v>
       </c>
+      <c r="BR40" s="3">
+        <v>0</v>
+      </c>
       <c r="BX40" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS40" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT40" s="2">
         <v>0</v>
       </c>
       <c r="CV40" s="1">
@@ -2589,6 +2493,9 @@
       <c r="Y41" s="1">
         <v>4</v>
       </c>
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
       <c r="AF41" s="3">
         <v>0</v>
       </c>
@@ -2601,9 +2508,6 @@
       <c r="AI41" s="3">
         <v>0</v>
       </c>
-      <c r="AJ41" s="3">
-        <v>0</v>
-      </c>
       <c r="AO41" s="2">
         <v>0</v>
       </c>
@@ -2664,9 +2568,6 @@
       <c r="BH41" s="2">
         <v>0</v>
       </c>
-      <c r="BM41" s="3">
-        <v>0</v>
-      </c>
       <c r="BN41" s="3">
         <v>0</v>
       </c>
@@ -2679,68 +2580,11 @@
       <c r="BQ41" s="3">
         <v>0</v>
       </c>
+      <c r="BR41" s="3">
+        <v>0</v>
+      </c>
       <c r="BX41" s="1">
         <v>4</v>
-      </c>
-      <c r="CA41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS41" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT41" s="2">
-        <v>0</v>
       </c>
       <c r="CV41" s="1">
         <v>0</v>
@@ -2750,70 +2594,10 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="C42" s="2">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="2">
-        <v>0</v>
-      </c>
-      <c r="R42" s="2">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
-        <v>0</v>
-      </c>
-      <c r="T42" s="2">
-        <v>0</v>
-      </c>
-      <c r="U42" s="2">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2">
-        <v>0</v>
-      </c>
       <c r="Y42" s="1">
         <v>0</v>
       </c>
-      <c r="AH42" s="1">
+      <c r="AG42" s="1">
         <v>0</v>
       </c>
       <c r="AO42" s="2">
@@ -2876,70 +2660,10 @@
       <c r="BH42" s="2">
         <v>0</v>
       </c>
-      <c r="BO42" s="1">
+      <c r="BP42" s="1">
         <v>0</v>
       </c>
       <c r="BX42" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS42" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT42" s="2">
         <v>0</v>
       </c>
       <c r="CV42" s="1">
@@ -2950,70 +2674,10 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="C43" s="2">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>0</v>
-      </c>
-      <c r="R43" s="2">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2">
-        <v>0</v>
-      </c>
-      <c r="U43" s="2">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2">
-        <v>0</v>
-      </c>
       <c r="Y43" s="1">
         <v>0</v>
       </c>
-      <c r="AH43" s="1">
+      <c r="AG43" s="1">
         <v>4</v>
       </c>
       <c r="AO43" s="2">
@@ -3076,70 +2740,10 @@
       <c r="BH43" s="2">
         <v>0</v>
       </c>
-      <c r="BO43" s="1">
+      <c r="BP43" s="1">
         <v>4</v>
       </c>
       <c r="BX43" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS43" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT43" s="2">
         <v>0</v>
       </c>
       <c r="CV43" s="1">
@@ -3150,70 +2754,10 @@
       <c r="A44" s="1">
         <v>0</v>
       </c>
-      <c r="C44" s="2">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2">
-        <v>0</v>
-      </c>
-      <c r="U44" s="2">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2">
-        <v>0</v>
-      </c>
       <c r="Y44" s="1">
         <v>4</v>
       </c>
-      <c r="AH44" s="1">
+      <c r="AG44" s="1">
         <v>0</v>
       </c>
       <c r="AO44" s="2">
@@ -3276,71 +2820,11 @@
       <c r="BH44" s="2">
         <v>0</v>
       </c>
-      <c r="BO44" s="1">
+      <c r="BP44" s="1">
         <v>0</v>
       </c>
       <c r="BX44" s="1">
         <v>4</v>
-      </c>
-      <c r="CA44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS44" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT44" s="2">
-        <v>0</v>
       </c>
       <c r="CV44" s="1">
         <v>0</v>
@@ -3350,70 +2834,10 @@
       <c r="A45" s="1">
         <v>0</v>
       </c>
-      <c r="C45" s="2">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
-        <v>0</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" s="2">
-        <v>0</v>
-      </c>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>0</v>
-      </c>
-      <c r="R45" s="2">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2">
-        <v>0</v>
-      </c>
-      <c r="U45" s="2">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2">
-        <v>0</v>
-      </c>
       <c r="Y45" s="1">
         <v>0</v>
       </c>
-      <c r="AH45" s="1">
+      <c r="AG45" s="1">
         <v>0</v>
       </c>
       <c r="AO45" s="2">
@@ -3476,70 +2900,10 @@
       <c r="BH45" s="2">
         <v>0</v>
       </c>
-      <c r="BO45" s="1">
+      <c r="BP45" s="1">
         <v>0</v>
       </c>
       <c r="BX45" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS45" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT45" s="2">
         <v>0</v>
       </c>
       <c r="CV45" s="1">
@@ -3550,67 +2914,7 @@
       <c r="A46" s="1">
         <v>0</v>
       </c>
-      <c r="C46" s="2">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2">
-        <v>0</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2">
-        <v>0</v>
-      </c>
-      <c r="O46" s="2">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2">
-        <v>0</v>
-      </c>
-      <c r="U46" s="2">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="1">
+      <c r="AG46" s="1">
         <v>4</v>
       </c>
       <c r="AO46" s="2">
@@ -3673,68 +2977,8 @@
       <c r="BH46" s="2">
         <v>0</v>
       </c>
-      <c r="BO46" s="1">
-        <v>4</v>
-      </c>
-      <c r="CA46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS46" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT46" s="2">
-        <v>0</v>
+      <c r="BP46" s="1">
+        <v>4</v>
       </c>
       <c r="CV46" s="1">
         <v>0</v>
@@ -3744,67 +2988,7 @@
       <c r="A47" s="1">
         <v>0</v>
       </c>
-      <c r="C47" s="2">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2">
-        <v>0</v>
-      </c>
-      <c r="K47" s="2">
-        <v>0</v>
-      </c>
-      <c r="L47" s="2">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-      <c r="N47" s="2">
-        <v>0</v>
-      </c>
-      <c r="O47" s="2">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>0</v>
-      </c>
-      <c r="R47" s="2">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2">
-        <v>0</v>
-      </c>
-      <c r="T47" s="2">
-        <v>0</v>
-      </c>
-      <c r="U47" s="2">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="1">
+      <c r="AG47" s="1">
         <v>0</v>
       </c>
       <c r="AO47" s="2">
@@ -3867,67 +3051,7 @@
       <c r="BH47" s="2">
         <v>0</v>
       </c>
-      <c r="BO47" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS47" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT47" s="2">
+      <c r="BP47" s="1">
         <v>0</v>
       </c>
       <c r="CV47" s="1">
@@ -3938,67 +3062,22 @@
       <c r="A48" s="1">
         <v>0</v>
       </c>
-      <c r="C48" s="2">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2">
-        <v>0</v>
-      </c>
-      <c r="U48" s="2">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="1">
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="1">
         <v>0</v>
       </c>
       <c r="AO48" s="2">
@@ -4061,67 +3140,7 @@
       <c r="BH48" s="2">
         <v>0</v>
       </c>
-      <c r="BO48" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS48" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT48" s="2">
+      <c r="BP48" s="1">
         <v>0</v>
       </c>
       <c r="CV48" s="1">
@@ -4132,67 +3151,22 @@
       <c r="A49" s="1">
         <v>0</v>
       </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2">
-        <v>0</v>
-      </c>
-      <c r="M49" s="2">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="2">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2">
-        <v>0</v>
-      </c>
-      <c r="U49" s="2">
-        <v>0</v>
-      </c>
-      <c r="V49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="1">
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="1">
         <v>4</v>
       </c>
       <c r="AO49" s="2">
@@ -4255,67 +3229,22 @@
       <c r="BH49" s="2">
         <v>0</v>
       </c>
-      <c r="BO49" s="1">
-        <v>4</v>
-      </c>
-      <c r="CA49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK49" s="2">
-        <v>13</v>
-      </c>
-      <c r="CL49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS49" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT49" s="2">
+      <c r="BP49" s="1">
+        <v>4</v>
+      </c>
+      <c r="CJ49" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL49" s="3">
+        <v>0</v>
+      </c>
+      <c r="CM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="CN49" s="3">
         <v>0</v>
       </c>
       <c r="CV49" s="1">
@@ -4326,67 +3255,22 @@
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="C50" s="2">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>0</v>
-      </c>
-      <c r="K50" s="2">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2">
-        <v>0</v>
-      </c>
-      <c r="M50" s="2">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2">
-        <v>0</v>
-      </c>
-      <c r="U50" s="2">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="1">
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <v>11</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="1">
         <v>0</v>
       </c>
       <c r="AO50" s="2">
@@ -4449,67 +3333,22 @@
       <c r="BH50" s="2">
         <v>0</v>
       </c>
-      <c r="BO50" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS50" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT50" s="2">
+      <c r="BP50" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="CM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="CN50" s="3">
         <v>0</v>
       </c>
       <c r="CV50">
@@ -4520,67 +3359,22 @@
       <c r="A51" s="1">
         <v>0</v>
       </c>
-      <c r="C51" s="2">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2">
-        <v>13</v>
-      </c>
-      <c r="N51" s="2">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="1">
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="1">
         <v>0</v>
       </c>
       <c r="AO51" s="2">
@@ -4643,67 +3437,22 @@
       <c r="BH51" s="2">
         <v>0</v>
       </c>
-      <c r="BO51" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS51" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT51" s="2">
+      <c r="BP51" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL51" s="3">
+        <v>11</v>
+      </c>
+      <c r="CM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="CN51" s="3">
         <v>0</v>
       </c>
       <c r="CV51" s="1">
@@ -4714,67 +3463,22 @@
       <c r="A52" s="1">
         <v>0</v>
       </c>
-      <c r="C52" s="2">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2">
-        <v>0</v>
-      </c>
-      <c r="M52" s="2">
-        <v>0</v>
-      </c>
-      <c r="N52" s="2">
-        <v>0</v>
-      </c>
-      <c r="O52" s="2">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2">
-        <v>0</v>
-      </c>
-      <c r="T52" s="2">
-        <v>0</v>
-      </c>
-      <c r="U52" s="2">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="1">
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="1">
         <v>4</v>
       </c>
       <c r="AO52" s="2">
@@ -4837,67 +3541,22 @@
       <c r="BH52" s="2">
         <v>0</v>
       </c>
-      <c r="BO52" s="1">
-        <v>4</v>
-      </c>
-      <c r="CA52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT52" s="2">
+      <c r="BP52" s="1">
+        <v>4</v>
+      </c>
+      <c r="CJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK52" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL52" s="3">
+        <v>0</v>
+      </c>
+      <c r="CM52" s="3">
+        <v>0</v>
+      </c>
+      <c r="CN52" s="3">
         <v>0</v>
       </c>
       <c r="CV52" s="1">
@@ -4908,70 +3567,10 @@
       <c r="A53" s="1">
         <v>0</v>
       </c>
-      <c r="C53" s="2">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>0</v>
-      </c>
-      <c r="K53" s="2">
-        <v>0</v>
-      </c>
-      <c r="L53" s="2">
-        <v>0</v>
-      </c>
-      <c r="M53" s="2">
-        <v>0</v>
-      </c>
-      <c r="N53" s="2">
-        <v>0</v>
-      </c>
-      <c r="O53" s="2">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2">
-        <v>0</v>
-      </c>
-      <c r="T53" s="2">
-        <v>0</v>
-      </c>
-      <c r="U53" s="2">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2">
-        <v>0</v>
-      </c>
       <c r="Y53" s="1">
         <v>0</v>
       </c>
-      <c r="AH53" s="1">
+      <c r="AG53" s="1">
         <v>0</v>
       </c>
       <c r="AO53" s="2">
@@ -5034,70 +3633,25 @@
       <c r="BH53" s="2">
         <v>0</v>
       </c>
-      <c r="BO53" s="1">
+      <c r="BP53" s="1">
         <v>0</v>
       </c>
       <c r="BX53" s="1">
         <v>0</v>
       </c>
-      <c r="CA53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT53" s="2">
+      <c r="CJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="CL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="CM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="CN53" s="3">
         <v>0</v>
       </c>
       <c r="CV53" s="1">
@@ -5108,70 +3662,10 @@
       <c r="A54" s="1">
         <v>0</v>
       </c>
-      <c r="C54" s="2">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2">
-        <v>0</v>
-      </c>
-      <c r="N54" s="2">
-        <v>0</v>
-      </c>
-      <c r="O54" s="2">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2">
-        <v>0</v>
-      </c>
-      <c r="T54" s="2">
-        <v>0</v>
-      </c>
-      <c r="U54" s="2">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2">
-        <v>0</v>
-      </c>
       <c r="Y54" s="1">
         <v>4</v>
       </c>
-      <c r="AH54" s="1">
+      <c r="AG54" s="1">
         <v>0</v>
       </c>
       <c r="AO54" s="2">
@@ -5234,71 +3728,11 @@
       <c r="BH54" s="2">
         <v>0</v>
       </c>
-      <c r="BO54" s="1">
+      <c r="BP54" s="1">
         <v>0</v>
       </c>
       <c r="BX54" s="1">
         <v>4</v>
-      </c>
-      <c r="CA54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT54" s="2">
-        <v>0</v>
       </c>
       <c r="CV54" s="1">
         <v>0</v>
@@ -5308,70 +3742,10 @@
       <c r="A55" s="1">
         <v>0</v>
       </c>
-      <c r="C55" s="2">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
-      <c r="K55" s="2">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>0</v>
-      </c>
-      <c r="N55" s="2">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2">
-        <v>0</v>
-      </c>
-      <c r="T55" s="2">
-        <v>0</v>
-      </c>
-      <c r="U55" s="2">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2">
-        <v>0</v>
-      </c>
       <c r="Y55" s="1">
         <v>0</v>
       </c>
-      <c r="AH55" s="1">
+      <c r="AG55" s="1">
         <v>4</v>
       </c>
       <c r="AO55" s="2">
@@ -5434,70 +3808,10 @@
       <c r="BH55" s="2">
         <v>0</v>
       </c>
-      <c r="BO55" s="1">
+      <c r="BP55" s="1">
         <v>4</v>
       </c>
       <c r="BX55" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT55" s="2">
         <v>0</v>
       </c>
       <c r="CV55" s="1">
@@ -5508,70 +3822,10 @@
       <c r="A56" s="1">
         <v>0</v>
       </c>
-      <c r="C56" s="2">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2">
-        <v>0</v>
-      </c>
-      <c r="L56" s="2">
-        <v>0</v>
-      </c>
-      <c r="M56" s="2">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2">
-        <v>0</v>
-      </c>
-      <c r="T56" s="2">
-        <v>0</v>
-      </c>
-      <c r="U56" s="2">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2">
-        <v>0</v>
-      </c>
       <c r="Y56" s="1">
         <v>0</v>
       </c>
-      <c r="AH56" s="1">
+      <c r="AG56" s="1">
         <v>0</v>
       </c>
       <c r="AO56" s="2">
@@ -5634,70 +3888,10 @@
       <c r="BH56" s="2">
         <v>0</v>
       </c>
-      <c r="BO56" s="1">
+      <c r="BP56" s="1">
         <v>0</v>
       </c>
       <c r="BX56" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT56" s="2">
         <v>0</v>
       </c>
       <c r="CV56" s="1">
@@ -5708,69 +3902,12 @@
       <c r="A57" s="1">
         <v>0</v>
       </c>
-      <c r="C57" s="2">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>0</v>
-      </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2">
-        <v>0</v>
-      </c>
       <c r="Y57" s="1">
         <v>4</v>
       </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
@@ -5783,9 +3920,6 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
-      <c r="AJ57" s="3">
-        <v>0</v>
-      </c>
       <c r="AO57" s="2">
         <v>0</v>
       </c>
@@ -5846,9 +3980,6 @@
       <c r="BH57" s="2">
         <v>0</v>
       </c>
-      <c r="BM57" s="3">
-        <v>0</v>
-      </c>
       <c r="BN57" s="3">
         <v>0</v>
       </c>
@@ -5861,68 +3992,11 @@
       <c r="BQ57" s="3">
         <v>0</v>
       </c>
+      <c r="BR57" s="3">
+        <v>0</v>
+      </c>
       <c r="BX57" s="1">
         <v>4</v>
-      </c>
-      <c r="CA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT57" s="2">
-        <v>0</v>
       </c>
       <c r="CV57" s="1">
         <v>0</v>
@@ -5932,69 +4006,12 @@
       <c r="A58" s="1">
         <v>0</v>
       </c>
-      <c r="C58" s="2">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
-      <c r="K58" s="2">
-        <v>0</v>
-      </c>
-      <c r="L58" s="2">
-        <v>0</v>
-      </c>
-      <c r="M58" s="2">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2">
-        <v>0</v>
-      </c>
-      <c r="O58" s="2">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
-        <v>0</v>
-      </c>
-      <c r="T58" s="2">
-        <v>0</v>
-      </c>
-      <c r="U58" s="2">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2">
-        <v>0</v>
-      </c>
       <c r="Y58" s="1">
         <v>0</v>
       </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
@@ -6007,9 +4024,6 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
-      </c>
       <c r="AO58" s="2">
         <v>0</v>
       </c>
@@ -6070,9 +4084,6 @@
       <c r="BH58" s="2">
         <v>0</v>
       </c>
-      <c r="BM58" s="3">
-        <v>0</v>
-      </c>
       <c r="BN58" s="3">
         <v>0</v>
       </c>
@@ -6085,67 +4096,10 @@
       <c r="BQ58" s="3">
         <v>0</v>
       </c>
+      <c r="BR58" s="3">
+        <v>0</v>
+      </c>
       <c r="BX58" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS58" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT58" s="2">
         <v>0</v>
       </c>
       <c r="CV58" s="1">
@@ -6156,220 +4110,100 @@
       <c r="A59" s="1">
         <v>0</v>
       </c>
-      <c r="C59" s="2">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0</v>
-      </c>
-      <c r="K59" s="2">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>0</v>
-      </c>
-      <c r="M59" s="2">
-        <v>0</v>
-      </c>
-      <c r="N59" s="2">
-        <v>0</v>
-      </c>
-      <c r="O59" s="2">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="2">
-        <v>0</v>
-      </c>
-      <c r="T59" s="2">
-        <v>0</v>
-      </c>
-      <c r="U59" s="2">
-        <v>0</v>
-      </c>
-      <c r="V59" s="2">
-        <v>0</v>
-      </c>
       <c r="Y59" s="1">
         <v>0</v>
       </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
       <c r="AF59" s="3">
         <v>0</v>
       </c>
       <c r="AG59" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN59" s="3">
+        <v>0</v>
+      </c>
+      <c r="BO59" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP59" s="3">
         <v>11</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM59" s="3">
-        <v>0</v>
-      </c>
-      <c r="BN59" s="3">
-        <v>0</v>
-      </c>
-      <c r="BO59" s="3">
-        <v>11</v>
-      </c>
-      <c r="BP59" s="3">
-        <v>0</v>
-      </c>
       <c r="BQ59" s="3">
         <v>0</v>
       </c>
+      <c r="BR59" s="3">
+        <v>0</v>
+      </c>
       <c r="BX59" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CM59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CP59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS59" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT59" s="2">
         <v>0</v>
       </c>
       <c r="CV59" s="1">
@@ -6380,69 +4214,12 @@
       <c r="A60" s="1">
         <v>0</v>
       </c>
-      <c r="C60" s="2">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0</v>
-      </c>
-      <c r="K60" s="2">
-        <v>0</v>
-      </c>
-      <c r="L60" s="2">
-        <v>0</v>
-      </c>
-      <c r="M60" s="2">
-        <v>0</v>
-      </c>
-      <c r="N60" s="2">
-        <v>0</v>
-      </c>
-      <c r="O60" s="2">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="2">
-        <v>0</v>
-      </c>
-      <c r="T60" s="2">
-        <v>0</v>
-      </c>
-      <c r="U60" s="2">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2">
-        <v>0</v>
-      </c>
       <c r="Y60" s="1">
         <v>4</v>
       </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
       <c r="AF60" s="3">
         <v>0</v>
       </c>
@@ -6455,9 +4232,6 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
-      <c r="AJ60" s="3">
-        <v>0</v>
-      </c>
       <c r="AO60" s="2">
         <v>0</v>
       </c>
@@ -6518,9 +4292,6 @@
       <c r="BH60" s="2">
         <v>0</v>
       </c>
-      <c r="BM60" s="3">
-        <v>0</v>
-      </c>
       <c r="BN60" s="3">
         <v>0</v>
       </c>
@@ -6531,6 +4302,9 @@
         <v>0</v>
       </c>
       <c r="BQ60" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR60" s="3">
         <v>0</v>
       </c>
       <c r="BX60" s="1">
@@ -6544,69 +4318,12 @@
       <c r="A61" s="1">
         <v>0</v>
       </c>
-      <c r="C61" s="2">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>0</v>
-      </c>
-      <c r="K61" s="2">
-        <v>0</v>
-      </c>
-      <c r="L61" s="2">
-        <v>0</v>
-      </c>
-      <c r="M61" s="2">
-        <v>0</v>
-      </c>
-      <c r="N61" s="2">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="2">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2">
-        <v>0</v>
-      </c>
-      <c r="S61" s="2">
-        <v>0</v>
-      </c>
-      <c r="T61" s="2">
-        <v>0</v>
-      </c>
-      <c r="U61" s="2">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2">
-        <v>0</v>
-      </c>
       <c r="Y61" s="1">
         <v>0</v>
       </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -6619,12 +4336,6 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="BM61" s="3">
-        <v>0</v>
-      </c>
       <c r="BN61" s="3">
         <v>0</v>
       </c>
@@ -6635,6 +4346,9 @@
         <v>0</v>
       </c>
       <c r="BQ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR61" s="3">
         <v>0</v>
       </c>
       <c r="BX61" s="1">
@@ -6651,10 +4365,10 @@
       <c r="Y62" s="1">
         <v>0</v>
       </c>
-      <c r="AH62" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO62" s="1">
+      <c r="AG62" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP62" s="1">
         <v>0</v>
       </c>
       <c r="BX62" s="1">
@@ -6671,10 +4385,10 @@
       <c r="Y63" s="1">
         <v>4</v>
       </c>
-      <c r="AH63" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO63" s="1">
+      <c r="AG63" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP63" s="1">
         <v>4</v>
       </c>
       <c r="BX63" s="1">
@@ -6691,10 +4405,10 @@
       <c r="Y64" s="1">
         <v>0</v>
       </c>
-      <c r="AH64" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO64" s="1">
+      <c r="AG64" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP64" s="1">
         <v>0</v>
       </c>
       <c r="BX64" s="1">
@@ -6711,21 +4425,15 @@
       <c r="Y65" s="1">
         <v>0</v>
       </c>
-      <c r="AH65" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO65" s="1">
+      <c r="AG65" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP65" s="1">
         <v>0</v>
       </c>
       <c r="BX65" s="1">
         <v>0</v>
       </c>
-      <c r="CD65" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE65" s="3">
-        <v>0</v>
-      </c>
       <c r="CF65" s="3">
         <v>0</v>
       </c>
@@ -6735,10 +4443,10 @@
       <c r="CH65" s="3">
         <v>0</v>
       </c>
-      <c r="CO65" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP65" s="3">
+      <c r="CI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ65" s="3">
         <v>0</v>
       </c>
       <c r="CQ65" s="3">
@@ -6748,6 +4456,12 @@
         <v>0</v>
       </c>
       <c r="CS65" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT65" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU65" s="3">
         <v>0</v>
       </c>
       <c r="CV65" s="1">
@@ -6761,21 +4475,15 @@
       <c r="Y66" s="1">
         <v>4</v>
       </c>
-      <c r="AH66" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO66" s="1">
+      <c r="AG66" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP66" s="1">
         <v>4</v>
       </c>
       <c r="BX66" s="1">
         <v>4</v>
       </c>
-      <c r="CD66" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE66" s="3">
-        <v>0</v>
-      </c>
       <c r="CF66" s="3">
         <v>0</v>
       </c>
@@ -6785,10 +4493,10 @@
       <c r="CH66" s="3">
         <v>0</v>
       </c>
-      <c r="CO66" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP66" s="3">
+      <c r="CI66" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ66" s="3">
         <v>0</v>
       </c>
       <c r="CQ66" s="3">
@@ -6798,6 +4506,12 @@
         <v>0</v>
       </c>
       <c r="CS66" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT66" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU66" s="3">
         <v>0</v>
       </c>
       <c r="CV66" s="1">
@@ -6811,61 +4525,61 @@
       <c r="Y67" s="1">
         <v>0</v>
       </c>
-      <c r="AH67" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO67" s="1">
+      <c r="AG67" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP67" s="1">
         <v>0</v>
       </c>
       <c r="BX67" s="1">
         <v>0</v>
       </c>
-      <c r="CD67" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE67" s="3">
-        <v>0</v>
-      </c>
       <c r="CF67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH67" s="3">
         <v>11</v>
       </c>
-      <c r="CG67" s="3">
-        <v>0</v>
-      </c>
-      <c r="CH67" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI67" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ67" s="1">
+      <c r="CI67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK67" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL67" s="1">
         <v>3</v>
       </c>
-      <c r="CK67" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL67" s="1">
-        <v>0</v>
-      </c>
       <c r="CM67" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN67" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO67" s="1">
         <v>3</v>
       </c>
-      <c r="CN67" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO67" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="3">
+      <c r="CP67" s="1">
         <v>0</v>
       </c>
       <c r="CQ67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS67" s="3">
         <v>11</v>
       </c>
-      <c r="CR67" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS67" s="3">
+      <c r="CT67" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU67" s="3">
         <v>0</v>
       </c>
       <c r="CV67" s="1">
@@ -6894,21 +4608,15 @@
       <c r="Y68" s="1">
         <v>0</v>
       </c>
-      <c r="AH68" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO68" s="1">
+      <c r="AG68" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP68" s="1">
         <v>0</v>
       </c>
       <c r="BX68" s="1">
         <v>0</v>
       </c>
-      <c r="CD68" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE68" s="3">
-        <v>0</v>
-      </c>
       <c r="CF68" s="3">
         <v>0</v>
       </c>
@@ -6918,10 +4626,10 @@
       <c r="CH68" s="3">
         <v>0</v>
       </c>
-      <c r="CO68" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP68" s="3">
+      <c r="CI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ68" s="3">
         <v>0</v>
       </c>
       <c r="CQ68" s="3">
@@ -6931,6 +4639,12 @@
         <v>0</v>
       </c>
       <c r="CS68" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT68" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU68" s="3">
         <v>0</v>
       </c>
       <c r="CV68" s="1">
@@ -6959,21 +4673,15 @@
       <c r="Y69" s="1">
         <v>4</v>
       </c>
-      <c r="AH69" s="1">
-        <v>4</v>
-      </c>
-      <c r="BO69" s="1">
+      <c r="AG69" s="1">
+        <v>4</v>
+      </c>
+      <c r="BP69" s="1">
         <v>4</v>
       </c>
       <c r="BX69" s="1">
         <v>4</v>
       </c>
-      <c r="CD69" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE69" s="3">
-        <v>0</v>
-      </c>
       <c r="CF69" s="3">
         <v>0</v>
       </c>
@@ -6983,10 +4691,10 @@
       <c r="CH69" s="3">
         <v>0</v>
       </c>
-      <c r="CO69" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP69" s="3">
+      <c r="CI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ69" s="3">
         <v>0</v>
       </c>
       <c r="CQ69" s="3">
@@ -6996,6 +4704,12 @@
         <v>0</v>
       </c>
       <c r="CS69" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT69" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU69" s="3">
         <v>0</v>
       </c>
       <c r="CV69" s="1">
@@ -7024,7 +4738,10 @@
       <c r="Y70" s="1">
         <v>0</v>
       </c>
-      <c r="AH70" s="1">
+      <c r="AG70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
         <v>0</v>
       </c>
       <c r="AO70" s="3">
@@ -7039,12 +4756,6 @@
       <c r="AR70" s="3">
         <v>0</v>
       </c>
-      <c r="AS70" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD70" s="3">
-        <v>0</v>
-      </c>
       <c r="BE70" s="3">
         <v>0</v>
       </c>
@@ -7057,16 +4768,16 @@
       <c r="BH70" s="3">
         <v>0</v>
       </c>
-      <c r="BO70" s="1">
+      <c r="BI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP70" s="1">
         <v>0</v>
       </c>
       <c r="BX70" s="1">
         <v>0</v>
       </c>
-      <c r="CF70" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ70" s="1">
+      <c r="CH70" s="1">
         <v>0</v>
       </c>
       <c r="CV70" s="1">
@@ -7095,7 +4806,10 @@
       <c r="Y71" s="1">
         <v>0</v>
       </c>
-      <c r="AH71" s="1">
+      <c r="AG71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
         <v>0</v>
       </c>
       <c r="AO71" s="3">
@@ -7110,12 +4824,6 @@
       <c r="AR71" s="3">
         <v>0</v>
       </c>
-      <c r="AS71" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD71" s="3">
-        <v>0</v>
-      </c>
       <c r="BE71" s="3">
         <v>0</v>
       </c>
@@ -7128,16 +4836,16 @@
       <c r="BH71" s="3">
         <v>0</v>
       </c>
-      <c r="BO71" s="1">
+      <c r="BI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP71" s="1">
         <v>0</v>
       </c>
       <c r="BX71" s="1">
         <v>0</v>
       </c>
-      <c r="CF71" s="1">
-        <v>4</v>
-      </c>
-      <c r="CQ71" s="1">
+      <c r="CH71" s="1">
         <v>4</v>
       </c>
       <c r="CV71" s="1">
@@ -7166,85 +4874,82 @@
       <c r="Y72" s="1">
         <v>4</v>
       </c>
+      <c r="AG72" s="1">
+        <v>4</v>
+      </c>
       <c r="AH72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="1">
         <v>3</v>
       </c>
-      <c r="AK72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL72" s="1">
-        <v>0</v>
-      </c>
       <c r="AM72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP72" s="3">
+        <v>11</v>
+      </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG72" s="3">
+        <v>11</v>
+      </c>
+      <c r="BH72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BJ72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK72" s="1">
         <v>3</v>
       </c>
-      <c r="AN72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="3">
-        <v>11</v>
-      </c>
-      <c r="AR72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF72" s="3">
-        <v>11</v>
-      </c>
-      <c r="BG72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH72" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ72" s="1">
+      <c r="BL72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN72" s="1">
         <v>3</v>
       </c>
-      <c r="BK72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL72" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM72" s="1">
-        <v>3</v>
-      </c>
-      <c r="BN72" s="1">
-        <v>0</v>
-      </c>
       <c r="BO72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP72" s="1">
         <v>4</v>
       </c>
       <c r="BX72" s="1">
         <v>4</v>
       </c>
-      <c r="CF72" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ72" s="1">
+      <c r="CH72" s="1">
         <v>0</v>
       </c>
       <c r="CV72" s="1">
@@ -7258,7 +4963,10 @@
       <c r="Y73" s="1">
         <v>0</v>
       </c>
-      <c r="AH73" s="1">
+      <c r="AG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
         <v>0</v>
       </c>
       <c r="AO73" s="3">
@@ -7273,12 +4981,6 @@
       <c r="AR73" s="3">
         <v>0</v>
       </c>
-      <c r="AS73" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD73" s="3">
-        <v>0</v>
-      </c>
       <c r="BE73" s="3">
         <v>0</v>
       </c>
@@ -7291,16 +4993,16 @@
       <c r="BH73" s="3">
         <v>0</v>
       </c>
-      <c r="BO73" s="1">
+      <c r="BI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="BP73" s="1">
         <v>0</v>
       </c>
       <c r="BX73" s="1">
         <v>0</v>
       </c>
-      <c r="CF73" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ73" s="1">
+      <c r="CH73" s="4">
         <v>0</v>
       </c>
       <c r="CV73" s="1">
@@ -7314,6 +5016,9 @@
       <c r="Y74" s="1">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
       <c r="AO74" s="3">
         <v>0</v>
       </c>
@@ -7326,12 +5031,6 @@
       <c r="AR74" s="3">
         <v>0</v>
       </c>
-      <c r="AS74" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD74" s="3">
-        <v>0</v>
-      </c>
       <c r="BE74" s="3">
         <v>0</v>
       </c>
@@ -7344,14 +5043,14 @@
       <c r="BH74" s="3">
         <v>0</v>
       </c>
+      <c r="BI74" s="3">
+        <v>0</v>
+      </c>
       <c r="BX74" s="1">
         <v>0</v>
       </c>
-      <c r="CF74" s="4">
+      <c r="CH74" s="4">
         <v>8</v>
-      </c>
-      <c r="CQ74" s="1">
-        <v>4</v>
       </c>
       <c r="CV74" s="1">
         <v>0</v>
@@ -7367,10 +5066,7 @@
       <c r="BX75" s="1">
         <v>4</v>
       </c>
-      <c r="CF75" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ75" s="1">
+      <c r="CH75" s="4">
         <v>0</v>
       </c>
       <c r="CV75" s="1">
@@ -7387,10 +5083,7 @@
       <c r="BX76" s="1">
         <v>0</v>
       </c>
-      <c r="CF76" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ76" s="1">
+      <c r="CH76" s="4">
         <v>0</v>
       </c>
       <c r="CV76" s="1">
@@ -7407,11 +5100,8 @@
       <c r="BX77" s="1">
         <v>0</v>
       </c>
-      <c r="CF77" s="4">
+      <c r="CH77" s="4">
         <v>8</v>
-      </c>
-      <c r="CQ77" s="1">
-        <v>4</v>
       </c>
       <c r="CV77" s="1">
         <v>0</v>
@@ -7427,10 +5117,7 @@
       <c r="BX78" s="1">
         <v>4</v>
       </c>
-      <c r="CF78" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ78" s="1">
+      <c r="CH78" s="4">
         <v>0</v>
       </c>
       <c r="CV78" s="1">
@@ -7447,10 +5134,7 @@
       <c r="BX79" s="1">
         <v>0</v>
       </c>
-      <c r="CF79" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ79" s="1">
+      <c r="CH79" s="1">
         <v>0</v>
       </c>
       <c r="CV79" s="1">
@@ -7467,10 +5151,7 @@
       <c r="BX80" s="1">
         <v>0</v>
       </c>
-      <c r="CF80" s="1">
-        <v>4</v>
-      </c>
-      <c r="CQ80" s="1">
+      <c r="CH80" s="1">
         <v>4</v>
       </c>
       <c r="CV80" s="1">
@@ -7487,10 +5168,7 @@
       <c r="BX81" s="1">
         <v>4</v>
       </c>
-      <c r="CF81" s="1">
-        <v>0</v>
-      </c>
-      <c r="CQ81" s="1">
+      <c r="CH81" s="1">
         <v>0</v>
       </c>
       <c r="CV81" s="1">
@@ -7507,12 +5185,6 @@
       <c r="BX82" s="1">
         <v>0</v>
       </c>
-      <c r="CD82" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE82" s="3">
-        <v>0</v>
-      </c>
       <c r="CF82" s="3">
         <v>0</v>
       </c>
@@ -7522,10 +5194,10 @@
       <c r="CH82" s="3">
         <v>0</v>
       </c>
-      <c r="CO82" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP82" s="3">
+      <c r="CI82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ82" s="3">
         <v>0</v>
       </c>
       <c r="CQ82" s="3">
@@ -7535,6 +5207,12 @@
         <v>0</v>
       </c>
       <c r="CS82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT82" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU82" s="3">
         <v>0</v>
       </c>
       <c r="CV82" s="1">
@@ -7551,12 +5229,6 @@
       <c r="BX83" s="1">
         <v>0</v>
       </c>
-      <c r="CD83" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE83" s="3">
-        <v>0</v>
-      </c>
       <c r="CF83" s="3">
         <v>0</v>
       </c>
@@ -7566,10 +5238,10 @@
       <c r="CH83" s="3">
         <v>0</v>
       </c>
-      <c r="CO83" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP83" s="3">
+      <c r="CI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ83" s="3">
         <v>0</v>
       </c>
       <c r="CQ83" s="3">
@@ -7579,6 +5251,12 @@
         <v>0</v>
       </c>
       <c r="CS83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT83" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU83" s="3">
         <v>0</v>
       </c>
       <c r="CV83" s="1">
@@ -7595,52 +5273,52 @@
       <c r="BX84" s="1">
         <v>4</v>
       </c>
-      <c r="CD84" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE84" s="3">
-        <v>0</v>
-      </c>
       <c r="CF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH84" s="3">
         <v>11</v>
       </c>
-      <c r="CG84" s="3">
-        <v>0</v>
-      </c>
-      <c r="CH84" s="3">
-        <v>0</v>
-      </c>
-      <c r="CI84" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ84" s="1">
+      <c r="CI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CK84" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL84" s="1">
         <v>3</v>
       </c>
-      <c r="CK84" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL84" s="1">
-        <v>0</v>
-      </c>
       <c r="CM84" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN84" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO84" s="1">
         <v>3</v>
       </c>
-      <c r="CN84" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO84" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP84" s="3">
+      <c r="CP84" s="1">
         <v>0</v>
       </c>
       <c r="CQ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CR84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CS84" s="3">
         <v>11</v>
       </c>
-      <c r="CR84" s="3">
-        <v>0</v>
-      </c>
-      <c r="CS84" s="3">
+      <c r="CT84" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU84" s="3">
         <v>0</v>
       </c>
       <c r="CV84" s="1">
@@ -7657,12 +5335,6 @@
       <c r="BX85" s="1">
         <v>0</v>
       </c>
-      <c r="CD85" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE85" s="3">
-        <v>0</v>
-      </c>
       <c r="CF85" s="3">
         <v>0</v>
       </c>
@@ -7672,10 +5344,10 @@
       <c r="CH85" s="3">
         <v>0</v>
       </c>
-      <c r="CO85" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP85" s="3">
+      <c r="CI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ85" s="3">
         <v>0</v>
       </c>
       <c r="CQ85" s="3">
@@ -7685,6 +5357,12 @@
         <v>0</v>
       </c>
       <c r="CS85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT85" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU85" s="3">
         <v>0</v>
       </c>
       <c r="CV85" s="1">
@@ -7770,12 +5448,6 @@
       <c r="BZ86" s="3">
         <v>0</v>
       </c>
-      <c r="CD86" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE86" s="3">
-        <v>0</v>
-      </c>
       <c r="CF86" s="3">
         <v>0</v>
       </c>
@@ -7785,10 +5457,10 @@
       <c r="CH86" s="3">
         <v>0</v>
       </c>
-      <c r="CO86" s="3">
-        <v>0</v>
-      </c>
-      <c r="CP86" s="3">
+      <c r="CI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CJ86" s="3">
         <v>0</v>
       </c>
       <c r="CQ86" s="3">
@@ -7798,6 +5470,12 @@
         <v>0</v>
       </c>
       <c r="CS86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CT86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CU86" s="3">
         <v>0</v>
       </c>
       <c r="CV86" s="1">

--- a/media/Levels/Level_2.xlsx
+++ b/media/Levels/Level_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD96424-AFD9-45C8-939F-12882C11B0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B404A2AE-D430-452C-ACC6-D3210B4ACD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="228" yWindow="144" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="228" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -810,6 +810,9 @@
       <c r="A11" s="1">
         <v>0</v>
       </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
       <c r="W11" s="3">
         <v>0</v>
       </c>
@@ -822,42 +825,6 @@
       <c r="Z11" s="3">
         <v>0</v>
       </c>
-      <c r="AA11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV11" s="3">
-        <v>0</v>
-      </c>
       <c r="BW11" s="3">
         <v>0</v>
       </c>
@@ -868,6 +835,9 @@
         <v>0</v>
       </c>
       <c r="BZ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA11" s="3">
         <v>0</v>
       </c>
       <c r="CN11" s="3">
@@ -893,6 +863,9 @@
       <c r="A12" s="1">
         <v>0</v>
       </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
       <c r="W12" s="3">
         <v>0</v>
       </c>
@@ -905,42 +878,6 @@
       <c r="Z12" s="3">
         <v>0</v>
       </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV12" s="3">
-        <v>0</v>
-      </c>
       <c r="BW12" s="3">
         <v>0</v>
       </c>
@@ -951,6 +888,9 @@
         <v>0</v>
       </c>
       <c r="BZ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA12" s="3">
         <v>0</v>
       </c>
       <c r="CN12" s="3">
@@ -976,70 +916,73 @@
       <c r="A13" s="1">
         <v>0</v>
       </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
       <c r="W13" s="3">
         <v>0</v>
       </c>
       <c r="X13" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y13" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="1">
         <v>0</v>
       </c>
       <c r="AB13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
         <v>3</v>
       </c>
-      <c r="AD13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="1">
-        <v>0</v>
-      </c>
       <c r="AF13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1">
         <v>3</v>
       </c>
-      <c r="AG13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="1">
-        <v>0</v>
-      </c>
       <c r="AI13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="1">
         <v>3</v>
       </c>
-      <c r="AJ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1">
-        <v>0</v>
-      </c>
       <c r="AL13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1">
         <v>3</v>
       </c>
-      <c r="AM13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3">
-        <v>11</v>
-      </c>
-      <c r="AQ13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="3">
+      <c r="AO13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>3</v>
+      </c>
+      <c r="AR13" s="1">
         <v>0</v>
       </c>
       <c r="AS13" s="1">
@@ -1078,70 +1021,73 @@
       <c r="BD13" s="1">
         <v>0</v>
       </c>
-      <c r="BE13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG13" s="3">
+      <c r="BE13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BJ13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU13" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV13" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX13" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY13" s="3">
         <v>11</v>
       </c>
-      <c r="BH13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BL13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BO13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BR13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT13" s="1">
-        <v>3</v>
-      </c>
-      <c r="BU13" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BW13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BX13" s="3">
-        <v>11</v>
-      </c>
-      <c r="BY13" s="3">
-        <v>0</v>
-      </c>
       <c r="BZ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA13" s="3">
         <v>0</v>
       </c>
       <c r="CN13" s="3">
@@ -1167,6 +1113,9 @@
       <c r="A14" s="1">
         <v>0</v>
       </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1179,42 +1128,6 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV14" s="3">
-        <v>0</v>
-      </c>
       <c r="BW14" s="3">
         <v>0</v>
       </c>
@@ -1225,6 +1138,9 @@
         <v>0</v>
       </c>
       <c r="BZ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA14" s="3">
         <v>0</v>
       </c>
       <c r="CN14" s="3">
@@ -1280,6 +1196,9 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
@@ -1292,42 +1211,6 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV15" s="3">
-        <v>0</v>
-      </c>
       <c r="BW15" s="3">
         <v>0</v>
       </c>
@@ -1338,6 +1221,9 @@
         <v>0</v>
       </c>
       <c r="BZ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA15" s="3">
         <v>0</v>
       </c>
       <c r="CN15" s="3">
@@ -1393,10 +1279,10 @@
       <c r="Q16" s="3">
         <v>0</v>
       </c>
-      <c r="Y16" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX16" s="1">
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY16" s="1">
         <v>0</v>
       </c>
       <c r="CV16" s="1">
@@ -1455,10 +1341,10 @@
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="Y17" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX17" s="1">
+      <c r="X17" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY17" s="1">
         <v>4</v>
       </c>
       <c r="CV17" s="1">
@@ -1499,10 +1385,10 @@
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX18" s="1">
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY18" s="1">
         <v>0</v>
       </c>
       <c r="CV18" s="1">
@@ -1543,10 +1429,10 @@
       <c r="Q19" s="3">
         <v>0</v>
       </c>
-      <c r="Y19" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX19" s="1">
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY19" s="1">
         <v>0</v>
       </c>
       <c r="CV19" s="1">
@@ -1560,10 +1446,10 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-      <c r="Y20" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX20" s="1">
+      <c r="X20" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY20" s="1">
         <v>4</v>
       </c>
       <c r="CV20" s="1">
@@ -1577,10 +1463,10 @@
       <c r="P21" s="1">
         <v>4</v>
       </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX21" s="1">
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY21" s="1">
         <v>0</v>
       </c>
       <c r="CV21" s="1">
@@ -1594,10 +1480,10 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX22" s="1">
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY22" s="1">
         <v>0</v>
       </c>
       <c r="CV22" s="1">
@@ -1611,10 +1497,10 @@
       <c r="P23" s="4">
         <v>0</v>
       </c>
-      <c r="Y23" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX23" s="1">
+      <c r="X23" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY23" s="1">
         <v>4</v>
       </c>
       <c r="CV23" s="1">
@@ -1628,10 +1514,10 @@
       <c r="P24" s="4">
         <v>8</v>
       </c>
-      <c r="Y24" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX24" s="1">
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY24" s="1">
         <v>0</v>
       </c>
       <c r="CV24" s="1">
@@ -1645,10 +1531,10 @@
       <c r="P25" s="4">
         <v>0</v>
       </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX25" s="1">
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY25" s="1">
         <v>0</v>
       </c>
       <c r="CV25" s="1">
@@ -1662,10 +1548,10 @@
       <c r="P26" s="4">
         <v>0</v>
       </c>
-      <c r="Y26" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX26" s="1">
+      <c r="X26" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY26" s="1">
         <v>4</v>
       </c>
       <c r="CV26" s="1">
@@ -1679,7 +1565,7 @@
       <c r="P27" s="4">
         <v>8</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="X27" s="1">
         <v>0</v>
       </c>
       <c r="AN27" s="3">
@@ -1697,9 +1583,6 @@
       <c r="AR27" s="3">
         <v>0</v>
       </c>
-      <c r="BE27" s="3">
-        <v>0</v>
-      </c>
       <c r="BF27" s="3">
         <v>0</v>
       </c>
@@ -1712,7 +1595,10 @@
       <c r="BI27" s="3">
         <v>0</v>
       </c>
-      <c r="BX27" s="1">
+      <c r="BJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY27" s="1">
         <v>0</v>
       </c>
       <c r="CV27" s="1">
@@ -1726,7 +1612,7 @@
       <c r="P28" s="4">
         <v>0</v>
       </c>
-      <c r="Y28" s="1">
+      <c r="X28" s="1">
         <v>0</v>
       </c>
       <c r="AG28" s="1">
@@ -1747,9 +1633,6 @@
       <c r="AR28" s="3">
         <v>0</v>
       </c>
-      <c r="BE28" s="3">
-        <v>0</v>
-      </c>
       <c r="BF28" s="3">
         <v>0</v>
       </c>
@@ -1762,10 +1645,13 @@
       <c r="BI28" s="3">
         <v>0</v>
       </c>
-      <c r="BP28" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX28" s="1">
+      <c r="BJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ28" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY28" s="1">
         <v>0</v>
       </c>
       <c r="CV28" s="1">
@@ -1779,7 +1665,7 @@
       <c r="P29" s="1">
         <v>0</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="X29" s="1">
         <v>4</v>
       </c>
       <c r="AG29" s="1">
@@ -1818,50 +1704,44 @@
       <c r="AR29" s="3">
         <v>0</v>
       </c>
-      <c r="BE29" s="3">
-        <v>0</v>
-      </c>
       <c r="BF29" s="3">
         <v>0</v>
       </c>
       <c r="BG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH29" s="3">
         <v>11</v>
       </c>
-      <c r="BH29" s="3">
-        <v>0</v>
-      </c>
       <c r="BI29" s="3">
         <v>0</v>
       </c>
-      <c r="BJ29" s="1">
+      <c r="BJ29" s="3">
         <v>0</v>
       </c>
       <c r="BK29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL29" s="1">
         <v>3</v>
       </c>
-      <c r="BL29" s="1">
-        <v>0</v>
-      </c>
       <c r="BM29" s="1">
         <v>0</v>
       </c>
       <c r="BN29" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO29" s="1">
         <v>3</v>
       </c>
-      <c r="BO29" s="1">
-        <v>0</v>
-      </c>
       <c r="BP29" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX29" s="1">
-        <v>4</v>
-      </c>
-      <c r="CC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD29" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="BQ29" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY29" s="1">
+        <v>4</v>
       </c>
       <c r="CE29" s="3">
         <v>0</v>
@@ -1870,6 +1750,12 @@
         <v>0</v>
       </c>
       <c r="CG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI29" s="3">
         <v>0</v>
       </c>
       <c r="CV29" s="1">
@@ -1883,7 +1769,7 @@
       <c r="P30" s="1">
         <v>4</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="X30" s="1">
         <v>0</v>
       </c>
       <c r="AG30" s="1">
@@ -1904,9 +1790,6 @@
       <c r="AR30" s="3">
         <v>0</v>
       </c>
-      <c r="BE30" s="3">
-        <v>0</v>
-      </c>
       <c r="BF30" s="3">
         <v>0</v>
       </c>
@@ -1919,16 +1802,13 @@
       <c r="BI30" s="3">
         <v>0</v>
       </c>
-      <c r="BP30" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX30" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC30" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD30" s="3">
+      <c r="BJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ30" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY30" s="1">
         <v>0</v>
       </c>
       <c r="CE30" s="3">
@@ -1938,6 +1818,12 @@
         <v>0</v>
       </c>
       <c r="CG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI30" s="3">
         <v>0</v>
       </c>
       <c r="CV30" s="1">
@@ -1951,7 +1837,7 @@
       <c r="P31" s="1">
         <v>0</v>
       </c>
-      <c r="Y31" s="1">
+      <c r="X31" s="1">
         <v>0</v>
       </c>
       <c r="AG31" s="1">
@@ -1972,9 +1858,6 @@
       <c r="AR31" s="3">
         <v>0</v>
       </c>
-      <c r="BE31" s="3">
-        <v>0</v>
-      </c>
       <c r="BF31" s="3">
         <v>0</v>
       </c>
@@ -1987,25 +1870,28 @@
       <c r="BI31" s="3">
         <v>0</v>
       </c>
-      <c r="BP31" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX31" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC31" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD31" s="3">
+      <c r="BJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ31" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY31" s="1">
         <v>0</v>
       </c>
       <c r="CE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="CG31" s="3">
         <v>11</v>
       </c>
-      <c r="CF31" s="3">
-        <v>0</v>
-      </c>
-      <c r="CG31" s="3">
+      <c r="CH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI31" s="3">
         <v>0</v>
       </c>
       <c r="CV31" s="1">
@@ -2046,23 +1932,17 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="1">
+      <c r="X32" s="1">
         <v>4</v>
       </c>
       <c r="AG32" s="1">
         <v>4</v>
       </c>
-      <c r="BP32" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX32" s="1">
-        <v>4</v>
-      </c>
-      <c r="CC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD32" s="3">
-        <v>0</v>
+      <c r="BQ32" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY32" s="1">
+        <v>4</v>
       </c>
       <c r="CE32" s="3">
         <v>0</v>
@@ -2071,6 +1951,12 @@
         <v>0</v>
       </c>
       <c r="CG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI32" s="3">
         <v>0</v>
       </c>
       <c r="CV32" s="1">
@@ -2111,22 +1997,16 @@
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="Y33" s="1">
+      <c r="X33" s="1">
         <v>0</v>
       </c>
       <c r="AG33" s="1">
         <v>0</v>
       </c>
-      <c r="BP33" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX33" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD33" s="3">
+      <c r="BQ33" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY33" s="1">
         <v>0</v>
       </c>
       <c r="CE33" s="3">
@@ -2136,6 +2016,12 @@
         <v>0</v>
       </c>
       <c r="CG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="CH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="CI33" s="3">
         <v>0</v>
       </c>
       <c r="CV33" s="1">
@@ -2194,16 +2080,16 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="Y34" s="1">
+      <c r="X34" s="1">
         <v>0</v>
       </c>
       <c r="AG34" s="1">
         <v>0</v>
       </c>
-      <c r="BP34" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX34" s="1">
+      <c r="BQ34" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY34" s="1">
         <v>0</v>
       </c>
       <c r="CV34" s="1">
@@ -2244,16 +2130,16 @@
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="Y35" s="1">
+      <c r="X35" s="1">
         <v>4</v>
       </c>
       <c r="AG35" s="1">
         <v>4</v>
       </c>
-      <c r="BP35" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX35" s="1">
+      <c r="BQ35" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY35" s="1">
         <v>4</v>
       </c>
       <c r="CV35" s="1">
@@ -2294,16 +2180,16 @@
       <c r="Q36" s="3">
         <v>0</v>
       </c>
-      <c r="Y36" s="1">
+      <c r="X36" s="1">
         <v>0</v>
       </c>
       <c r="AG36" s="1">
         <v>0</v>
       </c>
-      <c r="BP36" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX36" s="1">
+      <c r="BQ36" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY36" s="1">
         <v>0</v>
       </c>
       <c r="CV36" s="1">
@@ -2314,7 +2200,7 @@
       <c r="A37" s="1">
         <v>0</v>
       </c>
-      <c r="Y37" s="1">
+      <c r="X37" s="1">
         <v>0</v>
       </c>
       <c r="AE37" s="3">
@@ -2332,9 +2218,6 @@
       <c r="AI37" s="3">
         <v>0</v>
       </c>
-      <c r="BN37" s="3">
-        <v>0</v>
-      </c>
       <c r="BO37" s="3">
         <v>0</v>
       </c>
@@ -2347,7 +2230,10 @@
       <c r="BR37" s="3">
         <v>0</v>
       </c>
-      <c r="BX37" s="1">
+      <c r="BS37" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY37" s="1">
         <v>0</v>
       </c>
       <c r="CV37" s="1">
@@ -2358,7 +2244,7 @@
       <c r="A38" s="1">
         <v>0</v>
       </c>
-      <c r="Y38" s="1">
+      <c r="X38" s="1">
         <v>4</v>
       </c>
       <c r="AE38" s="3">
@@ -2376,9 +2262,6 @@
       <c r="AI38" s="3">
         <v>0</v>
       </c>
-      <c r="BN38" s="3">
-        <v>0</v>
-      </c>
       <c r="BO38" s="3">
         <v>0</v>
       </c>
@@ -2391,7 +2274,10 @@
       <c r="BR38" s="3">
         <v>0</v>
       </c>
-      <c r="BX38" s="1">
+      <c r="BS38" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY38" s="1">
         <v>4</v>
       </c>
       <c r="CV38" s="1">
@@ -2402,7 +2288,7 @@
       <c r="A39" s="1">
         <v>0</v>
       </c>
-      <c r="Y39" s="1">
+      <c r="X39" s="1">
         <v>0</v>
       </c>
       <c r="AE39" s="3">
@@ -2420,22 +2306,22 @@
       <c r="AI39" s="3">
         <v>0</v>
       </c>
-      <c r="BN39" s="3">
-        <v>0</v>
-      </c>
       <c r="BO39" s="3">
         <v>0</v>
       </c>
       <c r="BP39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ39" s="3">
         <v>11</v>
       </c>
-      <c r="BQ39" s="3">
-        <v>0</v>
-      </c>
       <c r="BR39" s="3">
         <v>0</v>
       </c>
-      <c r="BX39" s="1">
+      <c r="BS39" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY39" s="1">
         <v>0</v>
       </c>
       <c r="CV39" s="1">
@@ -2446,7 +2332,7 @@
       <c r="A40" s="1">
         <v>0</v>
       </c>
-      <c r="Y40" s="1">
+      <c r="X40" s="1">
         <v>0</v>
       </c>
       <c r="AE40" s="3">
@@ -2464,9 +2350,6 @@
       <c r="AI40" s="3">
         <v>0</v>
       </c>
-      <c r="BN40" s="3">
-        <v>0</v>
-      </c>
       <c r="BO40" s="3">
         <v>0</v>
       </c>
@@ -2479,7 +2362,10 @@
       <c r="BR40" s="3">
         <v>0</v>
       </c>
-      <c r="BX40" s="1">
+      <c r="BS40" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY40" s="1">
         <v>0</v>
       </c>
       <c r="CV40" s="1">
@@ -2490,7 +2376,7 @@
       <c r="A41" s="1">
         <v>0</v>
       </c>
-      <c r="Y41" s="1">
+      <c r="X41" s="1">
         <v>4</v>
       </c>
       <c r="AE41" s="3">
@@ -2568,9 +2454,6 @@
       <c r="BH41" s="2">
         <v>0</v>
       </c>
-      <c r="BN41" s="3">
-        <v>0</v>
-      </c>
       <c r="BO41" s="3">
         <v>0</v>
       </c>
@@ -2583,7 +2466,10 @@
       <c r="BR41" s="3">
         <v>0</v>
       </c>
-      <c r="BX41" s="1">
+      <c r="BS41" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY41" s="1">
         <v>4</v>
       </c>
       <c r="CV41" s="1">
@@ -2594,7 +2480,7 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="Y42" s="1">
+      <c r="X42" s="1">
         <v>0</v>
       </c>
       <c r="AG42" s="1">
@@ -2660,10 +2546,10 @@
       <c r="BH42" s="2">
         <v>0</v>
       </c>
-      <c r="BP42" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX42" s="1">
+      <c r="BQ42" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY42" s="1">
         <v>0</v>
       </c>
       <c r="CV42" s="1">
@@ -2674,7 +2560,7 @@
       <c r="A43" s="1">
         <v>0</v>
       </c>
-      <c r="Y43" s="1">
+      <c r="X43" s="1">
         <v>0</v>
       </c>
       <c r="AG43" s="1">
@@ -2740,10 +2626,10 @@
       <c r="BH43" s="2">
         <v>0</v>
       </c>
-      <c r="BP43" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX43" s="1">
+      <c r="BQ43" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY43" s="1">
         <v>0</v>
       </c>
       <c r="CV43" s="1">
@@ -2754,7 +2640,7 @@
       <c r="A44" s="1">
         <v>0</v>
       </c>
-      <c r="Y44" s="1">
+      <c r="X44" s="1">
         <v>4</v>
       </c>
       <c r="AG44" s="1">
@@ -2820,10 +2706,10 @@
       <c r="BH44" s="2">
         <v>0</v>
       </c>
-      <c r="BP44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX44" s="1">
+      <c r="BQ44" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY44" s="1">
         <v>4</v>
       </c>
       <c r="CV44" s="1">
@@ -2834,7 +2720,7 @@
       <c r="A45" s="1">
         <v>0</v>
       </c>
-      <c r="Y45" s="1">
+      <c r="X45" s="1">
         <v>0</v>
       </c>
       <c r="AG45" s="1">
@@ -2900,10 +2786,10 @@
       <c r="BH45" s="2">
         <v>0</v>
       </c>
-      <c r="BP45" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX45" s="1">
+      <c r="BQ45" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY45" s="1">
         <v>0</v>
       </c>
       <c r="CV45" s="1">
@@ -2977,7 +2863,7 @@
       <c r="BH46" s="2">
         <v>0</v>
       </c>
-      <c r="BP46" s="1">
+      <c r="BQ46" s="1">
         <v>4</v>
       </c>
       <c r="CV46" s="1">
@@ -3051,7 +2937,7 @@
       <c r="BH47" s="2">
         <v>0</v>
       </c>
-      <c r="BP47" s="1">
+      <c r="BQ47" s="1">
         <v>0</v>
       </c>
       <c r="CV47" s="1">
@@ -3140,7 +3026,7 @@
       <c r="BH48" s="2">
         <v>0</v>
       </c>
-      <c r="BP48" s="1">
+      <c r="BQ48" s="1">
         <v>0</v>
       </c>
       <c r="CV48" s="1">
@@ -3229,7 +3115,7 @@
       <c r="BH49" s="2">
         <v>0</v>
       </c>
-      <c r="BP49" s="1">
+      <c r="BQ49" s="1">
         <v>4</v>
       </c>
       <c r="CJ49" s="3">
@@ -3333,7 +3219,7 @@
       <c r="BH50" s="2">
         <v>0</v>
       </c>
-      <c r="BP50" s="1">
+      <c r="BQ50" s="1">
         <v>0</v>
       </c>
       <c r="CJ50" s="3">
@@ -3437,7 +3323,7 @@
       <c r="BH51" s="2">
         <v>0</v>
       </c>
-      <c r="BP51" s="1">
+      <c r="BQ51" s="1">
         <v>0</v>
       </c>
       <c r="CJ51" s="3">
@@ -3541,7 +3427,7 @@
       <c r="BH52" s="2">
         <v>0</v>
       </c>
-      <c r="BP52" s="1">
+      <c r="BQ52" s="1">
         <v>4</v>
       </c>
       <c r="CJ52" s="3">
@@ -3567,7 +3453,7 @@
       <c r="A53" s="1">
         <v>0</v>
       </c>
-      <c r="Y53" s="1">
+      <c r="X53" s="1">
         <v>0</v>
       </c>
       <c r="AG53" s="1">
@@ -3633,10 +3519,10 @@
       <c r="BH53" s="2">
         <v>0</v>
       </c>
-      <c r="BP53" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX53" s="1">
+      <c r="BQ53" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY53" s="1">
         <v>0</v>
       </c>
       <c r="CJ53" s="3">
@@ -3662,7 +3548,7 @@
       <c r="A54" s="1">
         <v>0</v>
       </c>
-      <c r="Y54" s="1">
+      <c r="X54" s="1">
         <v>4</v>
       </c>
       <c r="AG54" s="1">
@@ -3728,10 +3614,10 @@
       <c r="BH54" s="2">
         <v>0</v>
       </c>
-      <c r="BP54" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX54" s="1">
+      <c r="BQ54" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY54" s="1">
         <v>4</v>
       </c>
       <c r="CV54" s="1">
@@ -3742,7 +3628,7 @@
       <c r="A55" s="1">
         <v>0</v>
       </c>
-      <c r="Y55" s="1">
+      <c r="X55" s="1">
         <v>0</v>
       </c>
       <c r="AG55" s="1">
@@ -3808,10 +3694,10 @@
       <c r="BH55" s="2">
         <v>0</v>
       </c>
-      <c r="BP55" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX55" s="1">
+      <c r="BQ55" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY55" s="1">
         <v>0</v>
       </c>
       <c r="CV55" s="1">
@@ -3822,7 +3708,7 @@
       <c r="A56" s="1">
         <v>0</v>
       </c>
-      <c r="Y56" s="1">
+      <c r="X56" s="1">
         <v>0</v>
       </c>
       <c r="AG56" s="1">
@@ -3888,10 +3774,10 @@
       <c r="BH56" s="2">
         <v>0</v>
       </c>
-      <c r="BP56" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX56" s="1">
+      <c r="BQ56" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY56" s="1">
         <v>0</v>
       </c>
       <c r="CV56" s="1">
@@ -3902,7 +3788,7 @@
       <c r="A57" s="1">
         <v>0</v>
       </c>
-      <c r="Y57" s="1">
+      <c r="X57" s="1">
         <v>4</v>
       </c>
       <c r="AE57" s="3">
@@ -3980,9 +3866,6 @@
       <c r="BH57" s="2">
         <v>0</v>
       </c>
-      <c r="BN57" s="3">
-        <v>0</v>
-      </c>
       <c r="BO57" s="3">
         <v>0</v>
       </c>
@@ -3995,7 +3878,10 @@
       <c r="BR57" s="3">
         <v>0</v>
       </c>
-      <c r="BX57" s="1">
+      <c r="BS57" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY57" s="1">
         <v>4</v>
       </c>
       <c r="CV57" s="1">
@@ -4006,7 +3892,7 @@
       <c r="A58" s="1">
         <v>0</v>
       </c>
-      <c r="Y58" s="1">
+      <c r="X58" s="1">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
@@ -4084,9 +3970,6 @@
       <c r="BH58" s="2">
         <v>0</v>
       </c>
-      <c r="BN58" s="3">
-        <v>0</v>
-      </c>
       <c r="BO58" s="3">
         <v>0</v>
       </c>
@@ -4099,7 +3982,10 @@
       <c r="BR58" s="3">
         <v>0</v>
       </c>
-      <c r="BX58" s="1">
+      <c r="BS58" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY58" s="1">
         <v>0</v>
       </c>
       <c r="CV58" s="1">
@@ -4110,7 +3996,7 @@
       <c r="A59" s="1">
         <v>0</v>
       </c>
-      <c r="Y59" s="1">
+      <c r="X59" s="1">
         <v>0</v>
       </c>
       <c r="AE59" s="3">
@@ -4188,22 +4074,22 @@
       <c r="BH59" s="2">
         <v>0</v>
       </c>
-      <c r="BN59" s="3">
-        <v>0</v>
-      </c>
       <c r="BO59" s="3">
         <v>0</v>
       </c>
       <c r="BP59" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ59" s="3">
         <v>11</v>
       </c>
-      <c r="BQ59" s="3">
-        <v>0</v>
-      </c>
       <c r="BR59" s="3">
         <v>0</v>
       </c>
-      <c r="BX59" s="1">
+      <c r="BS59" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY59" s="1">
         <v>0</v>
       </c>
       <c r="CV59" s="1">
@@ -4214,7 +4100,7 @@
       <c r="A60" s="1">
         <v>0</v>
       </c>
-      <c r="Y60" s="1">
+      <c r="X60" s="1">
         <v>4</v>
       </c>
       <c r="AE60" s="3">
@@ -4292,9 +4178,6 @@
       <c r="BH60" s="2">
         <v>0</v>
       </c>
-      <c r="BN60" s="3">
-        <v>0</v>
-      </c>
       <c r="BO60" s="3">
         <v>0</v>
       </c>
@@ -4307,7 +4190,10 @@
       <c r="BR60" s="3">
         <v>0</v>
       </c>
-      <c r="BX60" s="1">
+      <c r="BS60" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY60" s="1">
         <v>4</v>
       </c>
       <c r="CV60" s="1">
@@ -4318,7 +4204,7 @@
       <c r="A61" s="1">
         <v>0</v>
       </c>
-      <c r="Y61" s="1">
+      <c r="X61" s="1">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
@@ -4336,9 +4222,6 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
-      <c r="BN61" s="3">
-        <v>0</v>
-      </c>
       <c r="BO61" s="3">
         <v>0</v>
       </c>
@@ -4351,7 +4234,10 @@
       <c r="BR61" s="3">
         <v>0</v>
       </c>
-      <c r="BX61" s="1">
+      <c r="BS61" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY61" s="1">
         <v>0</v>
       </c>
       <c r="CV61" s="1">
@@ -4362,16 +4248,16 @@
       <c r="A62" s="1">
         <v>0</v>
       </c>
-      <c r="Y62" s="1">
+      <c r="X62" s="1">
         <v>0</v>
       </c>
       <c r="AG62" s="1">
         <v>0</v>
       </c>
-      <c r="BP62" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX62" s="1">
+      <c r="BQ62" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY62" s="1">
         <v>0</v>
       </c>
       <c r="CV62" s="1">
@@ -4382,16 +4268,16 @@
       <c r="A63" s="1">
         <v>0</v>
       </c>
-      <c r="Y63" s="1">
+      <c r="X63" s="1">
         <v>4</v>
       </c>
       <c r="AG63" s="1">
         <v>4</v>
       </c>
-      <c r="BP63" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX63" s="1">
+      <c r="BQ63" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY63" s="1">
         <v>4</v>
       </c>
       <c r="CV63" s="1">
@@ -4402,16 +4288,16 @@
       <c r="A64" s="1">
         <v>0</v>
       </c>
-      <c r="Y64" s="1">
+      <c r="X64" s="1">
         <v>0</v>
       </c>
       <c r="AG64" s="1">
         <v>0</v>
       </c>
-      <c r="BP64" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX64" s="1">
+      <c r="BQ64" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY64" s="1">
         <v>0</v>
       </c>
       <c r="CV64" s="1">
@@ -4422,16 +4308,16 @@
       <c r="A65" s="1">
         <v>0</v>
       </c>
-      <c r="Y65" s="1">
+      <c r="X65" s="1">
         <v>0</v>
       </c>
       <c r="AG65" s="1">
         <v>0</v>
       </c>
-      <c r="BP65" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX65" s="1">
+      <c r="BQ65" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY65" s="1">
         <v>0</v>
       </c>
       <c r="CF65" s="3">
@@ -4472,16 +4358,16 @@
       <c r="A66" s="1">
         <v>0</v>
       </c>
-      <c r="Y66" s="1">
+      <c r="X66" s="1">
         <v>4</v>
       </c>
       <c r="AG66" s="1">
         <v>4</v>
       </c>
-      <c r="BP66" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX66" s="1">
+      <c r="BQ66" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY66" s="1">
         <v>4</v>
       </c>
       <c r="CF66" s="3">
@@ -4522,16 +4408,16 @@
       <c r="A67" s="1">
         <v>0</v>
       </c>
-      <c r="Y67" s="1">
+      <c r="X67" s="1">
         <v>0</v>
       </c>
       <c r="AG67" s="1">
         <v>0</v>
       </c>
-      <c r="BP67" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX67" s="1">
+      <c r="BQ67" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY67" s="1">
         <v>0</v>
       </c>
       <c r="CF67" s="3">
@@ -4590,6 +4476,12 @@
       <c r="A68" s="1">
         <v>0</v>
       </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
       <c r="P68" s="3">
         <v>0</v>
       </c>
@@ -4599,22 +4491,16 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-      <c r="S68" s="3">
-        <v>0</v>
-      </c>
-      <c r="T68" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="1">
+      <c r="X68" s="1">
         <v>0</v>
       </c>
       <c r="AG68" s="1">
         <v>0</v>
       </c>
-      <c r="BP68" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX68" s="1">
+      <c r="BQ68" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY68" s="1">
         <v>0</v>
       </c>
       <c r="CF68" s="3">
@@ -4655,6 +4541,12 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
       <c r="P69" s="3">
         <v>0</v>
       </c>
@@ -4664,22 +4556,16 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-      <c r="S69" s="3">
-        <v>0</v>
-      </c>
-      <c r="T69" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="1">
+      <c r="X69" s="1">
         <v>4</v>
       </c>
       <c r="AG69" s="1">
         <v>4</v>
       </c>
-      <c r="BP69" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX69" s="1">
+      <c r="BQ69" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY69" s="1">
         <v>4</v>
       </c>
       <c r="CF69" s="3">
@@ -4720,22 +4606,22 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>11</v>
-      </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="1">
+        <v>0</v>
+      </c>
+      <c r="X70" s="1">
         <v>0</v>
       </c>
       <c r="AG70" s="1">
@@ -4756,9 +4642,6 @@
       <c r="AR70" s="3">
         <v>0</v>
       </c>
-      <c r="BE70" s="3">
-        <v>0</v>
-      </c>
       <c r="BF70" s="3">
         <v>0</v>
       </c>
@@ -4771,10 +4654,13 @@
       <c r="BI70" s="3">
         <v>0</v>
       </c>
-      <c r="BP70" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX70" s="1">
+      <c r="BJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ70" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY70" s="1">
         <v>0</v>
       </c>
       <c r="CH70" s="1">
@@ -4788,6 +4674,12 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
       <c r="P71" s="3">
         <v>0</v>
       </c>
@@ -4797,13 +4689,7 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="3">
-        <v>0</v>
-      </c>
-      <c r="T71" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="1">
+      <c r="X71" s="1">
         <v>0</v>
       </c>
       <c r="AG71" s="1">
@@ -4824,9 +4710,6 @@
       <c r="AR71" s="3">
         <v>0</v>
       </c>
-      <c r="BE71" s="3">
-        <v>0</v>
-      </c>
       <c r="BF71" s="3">
         <v>0</v>
       </c>
@@ -4839,10 +4722,13 @@
       <c r="BI71" s="3">
         <v>0</v>
       </c>
-      <c r="BP71" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX71" s="1">
+      <c r="BJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ71" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY71" s="1">
         <v>0</v>
       </c>
       <c r="CH71" s="1">
@@ -4856,6 +4742,12 @@
       <c r="A72" s="1">
         <v>0</v>
       </c>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
@@ -4865,13 +4757,7 @@
       <c r="R72" s="3">
         <v>0</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="1">
+      <c r="X72" s="1">
         <v>4</v>
       </c>
       <c r="AG72" s="1">
@@ -4910,43 +4796,43 @@
       <c r="AR72" s="3">
         <v>0</v>
       </c>
-      <c r="BE72" s="3">
-        <v>0</v>
-      </c>
       <c r="BF72" s="3">
         <v>0</v>
       </c>
       <c r="BG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH72" s="3">
         <v>11</v>
       </c>
-      <c r="BH72" s="3">
-        <v>0</v>
-      </c>
       <c r="BI72" s="3">
         <v>0</v>
       </c>
-      <c r="BJ72" s="1">
+      <c r="BJ72" s="3">
         <v>0</v>
       </c>
       <c r="BK72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL72" s="1">
         <v>3</v>
       </c>
-      <c r="BL72" s="1">
-        <v>0</v>
-      </c>
       <c r="BM72" s="1">
         <v>0</v>
       </c>
       <c r="BN72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO72" s="1">
         <v>3</v>
       </c>
-      <c r="BO72" s="1">
-        <v>0</v>
-      </c>
       <c r="BP72" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ72" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY72" s="1">
         <v>4</v>
       </c>
       <c r="CH72" s="1">
@@ -4960,7 +4846,7 @@
       <c r="A73" s="1">
         <v>0</v>
       </c>
-      <c r="Y73" s="1">
+      <c r="X73" s="1">
         <v>0</v>
       </c>
       <c r="AG73" s="1">
@@ -4981,9 +4867,6 @@
       <c r="AR73" s="3">
         <v>0</v>
       </c>
-      <c r="BE73" s="3">
-        <v>0</v>
-      </c>
       <c r="BF73" s="3">
         <v>0</v>
       </c>
@@ -4996,10 +4879,13 @@
       <c r="BI73" s="3">
         <v>0</v>
       </c>
-      <c r="BP73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX73" s="1">
+      <c r="BJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="BQ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY73" s="1">
         <v>0</v>
       </c>
       <c r="CH73" s="4">
@@ -5013,7 +4899,7 @@
       <c r="A74" s="1">
         <v>0</v>
       </c>
-      <c r="Y74" s="1">
+      <c r="X74" s="1">
         <v>0</v>
       </c>
       <c r="AN74" s="3">
@@ -5031,9 +4917,6 @@
       <c r="AR74" s="3">
         <v>0</v>
       </c>
-      <c r="BE74" s="3">
-        <v>0</v>
-      </c>
       <c r="BF74" s="3">
         <v>0</v>
       </c>
@@ -5046,7 +4929,10 @@
       <c r="BI74" s="3">
         <v>0</v>
       </c>
-      <c r="BX74" s="1">
+      <c r="BJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY74" s="1">
         <v>0</v>
       </c>
       <c r="CH74" s="4">
@@ -5060,10 +4946,10 @@
       <c r="A75" s="1">
         <v>0</v>
       </c>
-      <c r="Y75" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX75" s="1">
+      <c r="X75" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY75" s="1">
         <v>4</v>
       </c>
       <c r="CH75" s="4">
@@ -5077,10 +4963,10 @@
       <c r="A76" s="1">
         <v>0</v>
       </c>
-      <c r="Y76" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX76" s="1">
+      <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY76" s="1">
         <v>0</v>
       </c>
       <c r="CH76" s="4">
@@ -5094,10 +4980,10 @@
       <c r="A77" s="1">
         <v>0</v>
       </c>
-      <c r="Y77" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX77" s="1">
+      <c r="X77" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY77" s="1">
         <v>0</v>
       </c>
       <c r="CH77" s="4">
@@ -5111,10 +4997,10 @@
       <c r="A78" s="1">
         <v>0</v>
       </c>
-      <c r="Y78" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX78" s="1">
+      <c r="X78" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY78" s="1">
         <v>4</v>
       </c>
       <c r="CH78" s="4">
@@ -5128,10 +5014,10 @@
       <c r="A79" s="1">
         <v>0</v>
       </c>
-      <c r="Y79" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX79" s="1">
+      <c r="X79" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY79" s="1">
         <v>0</v>
       </c>
       <c r="CH79" s="1">
@@ -5145,10 +5031,10 @@
       <c r="A80" s="1">
         <v>0</v>
       </c>
-      <c r="Y80" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX80" s="1">
+      <c r="X80" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY80" s="1">
         <v>0</v>
       </c>
       <c r="CH80" s="1">
@@ -5162,10 +5048,10 @@
       <c r="A81" s="1">
         <v>0</v>
       </c>
-      <c r="Y81" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX81" s="1">
+      <c r="X81" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY81" s="1">
         <v>4</v>
       </c>
       <c r="CH81" s="1">
@@ -5179,10 +5065,10 @@
       <c r="A82" s="1">
         <v>0</v>
       </c>
-      <c r="Y82" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX82" s="1">
+      <c r="X82" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY82" s="1">
         <v>0</v>
       </c>
       <c r="CF82" s="3">
@@ -5223,10 +5109,10 @@
       <c r="A83" s="1">
         <v>0</v>
       </c>
-      <c r="Y83" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX83" s="1">
+      <c r="X83" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY83" s="1">
         <v>0</v>
       </c>
       <c r="CF83" s="3">
@@ -5267,10 +5153,10 @@
       <c r="A84" s="1">
         <v>0</v>
       </c>
-      <c r="Y84" s="1">
-        <v>4</v>
-      </c>
-      <c r="BX84" s="1">
+      <c r="X84" s="1">
+        <v>4</v>
+      </c>
+      <c r="BY84" s="1">
         <v>4</v>
       </c>
       <c r="CF84" s="3">
@@ -5329,10 +5215,10 @@
       <c r="A85" s="1">
         <v>0</v>
       </c>
-      <c r="Y85" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX85" s="1">
+      <c r="X85" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY85" s="1">
         <v>0</v>
       </c>
       <c r="CF85" s="3">
@@ -5388,6 +5274,9 @@
       <c r="I86" s="3">
         <v>0</v>
       </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
       <c r="W86" s="3">
         <v>0</v>
       </c>
@@ -5400,42 +5289,6 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-      <c r="AA86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI86" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV86" s="3">
-        <v>0</v>
-      </c>
       <c r="BW86" s="3">
         <v>0</v>
       </c>
@@ -5446,6 +5299,9 @@
         <v>0</v>
       </c>
       <c r="BZ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA86" s="3">
         <v>0</v>
       </c>
       <c r="CF86" s="3">
@@ -5501,6 +5357,9 @@
       <c r="I87" s="3">
         <v>0</v>
       </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
       <c r="W87" s="3">
         <v>0</v>
       </c>
@@ -5513,42 +5372,6 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-      <c r="AA87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI87" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV87" s="3">
-        <v>0</v>
-      </c>
       <c r="BW87" s="3">
         <v>0</v>
       </c>
@@ -5559,6 +5382,9 @@
         <v>0</v>
       </c>
       <c r="BZ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA87" s="3">
         <v>0</v>
       </c>
       <c r="CV87" s="1">
@@ -5584,70 +5410,73 @@
       <c r="I88" s="3">
         <v>0</v>
       </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
       <c r="W88" s="3">
         <v>0</v>
       </c>
       <c r="X88" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y88" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-      <c r="AA88" s="3">
+      <c r="AA88" s="1">
         <v>0</v>
       </c>
       <c r="AB88" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1">
         <v>3</v>
       </c>
-      <c r="AD88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="1">
-        <v>0</v>
-      </c>
       <c r="AF88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="1">
         <v>3</v>
       </c>
-      <c r="AG88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH88" s="1">
-        <v>0</v>
-      </c>
       <c r="AI88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="1">
         <v>3</v>
       </c>
-      <c r="AJ88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK88" s="1">
-        <v>0</v>
-      </c>
       <c r="AL88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="1">
         <v>3</v>
       </c>
-      <c r="AM88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP88" s="3">
-        <v>11</v>
-      </c>
-      <c r="AQ88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR88" s="3">
+      <c r="AO88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="1">
+        <v>3</v>
+      </c>
+      <c r="AR88" s="1">
         <v>0</v>
       </c>
       <c r="AS88" s="1">
@@ -5686,70 +5515,73 @@
       <c r="BD88" s="1">
         <v>0</v>
       </c>
-      <c r="BE88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG88" s="3">
+      <c r="BE88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BJ88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU88" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV88" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW88" s="3">
+        <v>0</v>
+      </c>
+      <c r="BX88" s="3">
+        <v>0</v>
+      </c>
+      <c r="BY88" s="3">
         <v>11</v>
       </c>
-      <c r="BH88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK88" s="1">
-        <v>3</v>
-      </c>
-      <c r="BL88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN88" s="1">
-        <v>3</v>
-      </c>
-      <c r="BO88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ88" s="1">
-        <v>3</v>
-      </c>
-      <c r="BR88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT88" s="1">
-        <v>3</v>
-      </c>
-      <c r="BU88" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BW88" s="3">
-        <v>0</v>
-      </c>
-      <c r="BX88" s="3">
-        <v>11</v>
-      </c>
-      <c r="BY88" s="3">
-        <v>0</v>
-      </c>
       <c r="BZ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA88" s="3">
         <v>0</v>
       </c>
       <c r="CV88" s="1">
@@ -5775,6 +5607,9 @@
       <c r="I89" s="3">
         <v>0</v>
       </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
@@ -5787,42 +5622,6 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI89" s="3">
-        <v>0</v>
-      </c>
-      <c r="BV89" s="3">
-        <v>0</v>
-      </c>
       <c r="BW89" s="3">
         <v>0</v>
       </c>
@@ -5833,6 +5632,9 @@
         <v>0</v>
       </c>
       <c r="BZ89" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA89" s="3">
         <v>0</v>
       </c>
       <c r="CV89" s="1">
@@ -5858,6 +5660,9 @@
       <c r="I90" s="3">
         <v>0</v>
       </c>
+      <c r="V90" s="3">
+        <v>0</v>
+      </c>
       <c r="W90" s="3">
         <v>0</v>
       </c>
@@ -5870,45 +5675,9 @@
       <c r="Z90" s="3">
         <v>0</v>
       </c>
-      <c r="AA90" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN90" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO90" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP90" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ90" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR90" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE90" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF90" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG90" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH90" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI90" s="3">
-        <v>0</v>
-      </c>
       <c r="BK90" t="s">
         <v>0</v>
       </c>
-      <c r="BV90" s="3">
-        <v>0</v>
-      </c>
       <c r="BW90" s="3">
         <v>0</v>
       </c>
@@ -5919,6 +5688,9 @@
         <v>0</v>
       </c>
       <c r="BZ90" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA90" s="3">
         <v>0</v>
       </c>
       <c r="CV90" s="1">
